--- a/indicadores/GR-EPUB_out.xlsx
+++ b/indicadores/GR-EPUB_out.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Correlograma" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Referencias" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Correlograma" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="190">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -55,7 +56,7 @@
     <t xml:space="preserve">Modelo</t>
   </si>
   <si>
-    <t xml:space="preserve">niv</t>
+    <t xml:space="preserve">log</t>
   </si>
   <si>
     <t xml:space="preserve">(1 0 2)(1 0 0)</t>
@@ -106,13 +107,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">18/11/2025</t>
+    <t xml:space="preserve">07/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">vcorvalan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -494,6 +495,63 @@
   </si>
   <si>
     <t xml:space="preserve">2030T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencias de las series incluidas en la hoja Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original | serie de datos brutos transformados, se importa directo desde base de datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_normal | serie original con 4 forecasts obtenidos del mejor modelo ARIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_optimista | serie original con 4 forecasts, intervalo y límite optimista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_pesimista | serie original con 4 forecasts, intervalo y límite pesimista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b_d16 | salida D16 del X13-ARIMA-SEATS con los factores estacionales de la serie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_c17 | salida C17 del X13-ARIMA-SEATS con pesos del irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_d12 | salida D12 del X13-ARIMA-SEATS con el componente tendencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_hp_1600 | tendencia HP de largo plazo con un lambda de 1.600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_hp_200 | suavizado con filtro HP usando lambda de 200, sirve para determinar PG automáticos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e_ajustada | serie ajustada por estacionalidad usando el mejor modelo (LOG o NIV según el caso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f_filtrada | serie ajustada por estacionalidad y corregida por irregularidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_final | serie f_filtrada con o sin suavizado 2x2 según el caso (es la vieja española)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_final_fct_normal | a_original_fct ajustada por D16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_final_tctl | tasas de cambio trimestral logarítmicas de la serie g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_var_interanual | variaciones interanuales de g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_final_var_trimestral | variaciones trimestrales de g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h_irregular | g_final/d_d12 componente irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i_dt | g_final/d_hp_1600 desvíos respecto de la tendencia</t>
   </si>
   <si>
     <t xml:space="preserve">Coeficientes de correlación de TCTL del ICA-SFE y serie específica</t>
@@ -1060,7 +1118,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>-0.3395248383724</v>
+        <v>-0.386959165100972</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1118,7 +1176,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.00446736361239215</v>
+        <v>0.00861123517101566</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1188,7 +1246,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.81652422565032</v>
+        <v>0.624680655539973</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1218,7 +1276,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.416396819700786</v>
+        <v>0.145530738030723</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1478,40 +1536,40 @@
         <v>61.655</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>-5.83011546545712</v>
+        <v>0.912068749050234</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>68.3906576499527</v>
+        <v>68.5129890185091</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>68.1953359760671</v>
+        <v>68.2161255338701</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>68.4649200887491</v>
+        <v>68.7182643027017</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>67.4851154654571</v>
+        <v>67.5990708641243</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>67.4851154654571</v>
+        <v>67.5990708641243</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>67.6370008578184</v>
+        <v>67.7699855752383</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>67.6370008578184</v>
+        <v>67.7699855752383</v>
       </c>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="18" t="n">
-        <v>0.98898012070608</v>
+        <v>0.989155290786247</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>0.991812708152877</v>
+        <v>0.993459904749204</v>
       </c>
     </row>
     <row r="3">
@@ -1531,44 +1589,44 @@
         <v>68.596</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.655228357458992</v>
+        <v>1.00710867861254</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>66.4955652648208</v>
+        <v>66.6698231412458</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>67.461448093274</v>
+        <v>67.4354151223726</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>67.9173664430343</v>
+        <v>68.0939583984989</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>67.940771642541</v>
+        <v>68.1118149974662</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>67.940771642541</v>
+        <v>68.1118149974662</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>66.7075090345378</v>
+        <v>66.8671451229149</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>66.7075090345378</v>
+        <v>66.8671451229149</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>-0.0138376574618262</v>
+        <v>-0.0134116640875042</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17" t="n">
-        <v>-0.0137423571638627</v>
+        <v>-0.0133221284416694</v>
       </c>
       <c r="R3" s="18" t="n">
-        <v>1.00318733691296</v>
+        <v>1.00295968959226</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>0.988824149495075</v>
+        <v>0.991573122247019</v>
       </c>
     </row>
     <row r="4">
@@ -1588,44 +1646,44 @@
         <v>67.922</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>4.45862261238799</v>
+        <v>1.06718613038395</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>65.6122102136989</v>
+        <v>65.6951861357774</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>66.7271163226617</v>
+        <v>66.6543190517066</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>67.364913774203</v>
+        <v>67.4640565271032</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>63.463377387612</v>
+        <v>63.6458796326028</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>63.463377387612</v>
+        <v>63.6458796326028</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>65.9049689916216</v>
+        <v>65.9971382929823</v>
       </c>
       <c r="N4" s="14" t="n">
-        <v>65.9049689916216</v>
+        <v>65.9971382929823</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>-0.0121036851502985</v>
+        <v>-0.0130963603225658</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17" t="n">
-        <v>-0.0120307301911198</v>
+        <v>-0.0130109761428178</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>1.00446195573917</v>
+        <v>1.00459626001486</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.987678962071962</v>
+        <v>0.990140462492543</v>
       </c>
     </row>
     <row r="5">
@@ -1645,44 +1703,44 @@
         <v>69.42</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.667650451278703</v>
+        <v>1.01217498501891</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>67.8766929260983</v>
+        <v>67.8648574570971</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>65.9921963536295</v>
+        <v>65.8728744126253</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>66.8027800851362</v>
+        <v>66.8230520043165</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>68.7523495487213</v>
+        <v>68.5849789092575</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>68.7523495487213</v>
+        <v>68.5849789092575</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>67.5525312187813</v>
+        <v>67.5547653913786</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>67.5525312187813</v>
+        <v>67.5547653913786</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>0.0246916948216176</v>
+        <v>0.0233272261631944</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17" t="n">
-        <v>0.0249990592874589</v>
+        <v>0.0236014339209909</v>
       </c>
       <c r="R5" s="18" t="n">
-        <v>0.995224256024524</v>
+        <v>0.995430741663099</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>1.02364423297552</v>
+        <v>1.02553237571232</v>
       </c>
     </row>
     <row r="6">
@@ -1702,46 +1760,46 @@
         <v>63.243</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-5.99904839007053</v>
+        <v>0.91124008728697</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>67.4741356849268</v>
+        <v>67.5373102603733</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>65.2545040387421</v>
+        <v>65.0892380212452</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>66.2066756967823</v>
+        <v>66.1463472614684</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>69.2420483900705</v>
+        <v>69.4032241143967</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>69.2420483900705</v>
+        <v>69.4032241143967</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>67.3700113163942</v>
+        <v>67.443380505377</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>67.3700113163942</v>
+        <v>67.443380505377</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>-0.00270555253843968</v>
+        <v>-0.00165016949732773</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>-0.00394738882620516</v>
+        <v>-0.00481931738791253</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>-0.0027018958297198</v>
+        <v>-0.00164880871625217</v>
       </c>
       <c r="R6" s="18" t="n">
-        <v>0.998456825456516</v>
+        <v>0.998609216822017</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>1.03241932965112</v>
+        <v>1.03616792200522</v>
       </c>
     </row>
     <row r="7">
@@ -1761,46 +1819,46 @@
         <v>63.349</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1.27795515779593</v>
+        <v>1.01549972180879</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.950767763086892</v>
+        <v>1</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>65.5759453978106</v>
+        <v>65.6626104075613</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>64.5135803263111</v>
+        <v>64.3032617589931</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>65.5620587774071</v>
+        <v>65.4181543644129</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>62.0710448422041</v>
+        <v>62.3820948834569</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>62.2435989367146</v>
+        <v>62.3820948834569</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>65.7675094293036</v>
+        <v>65.8456135910425</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>65.7675094293036</v>
+        <v>65.8456135910425</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>-0.0240740442335705</v>
+        <v>-0.0239756247174051</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>-0.0140913612101381</v>
+        <v>-0.0152770322404909</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>-0.0237865758930147</v>
+        <v>-0.0236904927119874</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>1.00292125459009</v>
+        <v>1.00278702266549</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>1.01943666894087</v>
+        <v>1.02398559248565</v>
       </c>
     </row>
     <row r="8">
@@ -1820,46 +1878,46 @@
         <v>73.472</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>4.13120854628541</v>
+        <v>1.06150338838846</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>67.2726491360309</v>
+        <v>67.2205199801498</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>63.7714583798678</v>
+        <v>63.5174937486039</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>64.8695643587431</v>
+        <v>64.6389697632689</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>69.3407914537146</v>
+        <v>69.2150404828597</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>69.3407914537146</v>
+        <v>69.2150404828597</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>67.0078403342344</v>
+        <v>66.9325472226003</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>67.0078403342344</v>
+        <v>66.9325472226003</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>0.0186836937458429</v>
+        <v>0.0163725405606158</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>0.0167342669223176</v>
+        <v>0.0141734771205591</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>0.0188593260668348</v>
+        <v>0.0165073050774271</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>0.99606364837423</v>
+        <v>0.995715999256855</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>1.05074969330462</v>
+        <v>1.05376555768263</v>
       </c>
     </row>
     <row r="9">
@@ -1879,46 +1937,46 @@
         <v>67.4</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.29382050720598</v>
+        <v>1.00720264898598</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>66.5521939312004</v>
+        <v>66.1322427663901</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>63.0287526245751</v>
+        <v>62.7332813835154</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>64.1132351733195</v>
+        <v>63.7941096107503</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>67.106179492794</v>
+        <v>66.9180130412248</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>67.106179492794</v>
+        <v>66.9180130412248</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>66.0067434187039</v>
+        <v>65.6803752390136</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>66.0067434187039</v>
+        <v>65.6803752390136</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>-0.0150527226408333</v>
+        <v>-0.0188851761307047</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>-0.0228827517220799</v>
+        <v>-0.027746231394718</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>-0.0149399967307873</v>
+        <v>-0.0187079684779111</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>0.9918041693252</v>
+        <v>0.993167213019332</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1.04724813152922</v>
+        <v>1.04697815562175</v>
       </c>
     </row>
     <row r="10">
@@ -1938,46 +1996,46 @@
         <v>54.461</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-6.01282323551279</v>
+        <v>0.912696556612417</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>62.09573549001</v>
+        <v>61.7172368289237</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>62.2895583187668</v>
+        <v>61.9555330238745</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>63.29947008914</v>
+        <v>62.8917704131692</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>60.4738232355128</v>
+        <v>59.6704343907449</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>60.4738232355128</v>
+        <v>59.6704343907449</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>62.4818800225689</v>
+        <v>62.1530127442331</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>62.4818800225689</v>
+        <v>62.1530127442331</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>-0.0548803147491478</v>
+        <v>-0.0552008861158951</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>-0.0725564861622012</v>
+        <v>-0.0784416160859859</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>-0.0534015649548937</v>
+        <v>-0.053704968675106</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>1.00621853545194</v>
+        <v>1.00706084617037</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>1.00308754322543</v>
+        <v>1.0031874428436</v>
       </c>
     </row>
     <row r="11">
@@ -1997,46 +2055,46 @@
         <v>64.203</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>2.32930587354384</v>
+        <v>1.02966699000025</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>61.3291074179112</v>
+        <v>61.4892203372124</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>61.5605191125694</v>
+        <v>61.1917724871139</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>62.4496326958059</v>
+        <v>61.9557681939899</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>61.8736941264562</v>
+        <v>62.3531691542179</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>61.8736941264562</v>
+        <v>62.3531691542179</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>61.4670187176802</v>
+        <v>61.5870886953201</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>61.4670187176802</v>
+        <v>61.5870886953201</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>-0.0163758451195883</v>
+        <v>-0.00914704268306189</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>-0.0653892894674107</v>
+        <v>-0.0646743900386667</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>-0.0162424898950254</v>
+        <v>-0.00910533575004402</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>1.0022487087384</v>
+        <v>1.00159163439658</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>0.998481162988274</v>
+        <v>1.0064602836646</v>
       </c>
     </row>
     <row r="12">
@@ -2056,46 +2114,46 @@
         <v>64.839</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3.19213661770443</v>
+        <v>1.04626988405914</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>60.5137374669543</v>
+        <v>60.8638436174968</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>60.8471438216825</v>
+        <v>60.4480954040206</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>61.5709583486504</v>
+        <v>60.9938122965646</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>61.6468633822956</v>
+        <v>61.9715820820998</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>61.6468633822956</v>
+        <v>61.9715820820998</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>60.6796438567811</v>
+        <v>60.8983828306202</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>60.6796438567811</v>
+        <v>60.8983828306202</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>-0.0128924646886246</v>
+        <v>-0.0112456296107084</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>-0.0944396423745099</v>
+        <v>-0.0901529172632867</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>-0.0128097128724516</v>
+        <v>-0.0111826338813821</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>1.00274163184711</v>
+        <v>1.00056748327201</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>0.997247200864641</v>
+        <v>1.00744915821731</v>
       </c>
     </row>
     <row r="13">
@@ -2115,46 +2173,46 @@
         <v>57.621</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.0698454639229605</v>
+        <v>1.0056512710432</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>59.1808872162843</v>
+        <v>59.1985446966811</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>60.1551369961893</v>
+        <v>59.7313232782986</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>60.6678027101598</v>
+        <v>60.0155990690466</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>57.551154536077</v>
+        <v>57.2971980040631</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>57.551154536077</v>
+        <v>57.2971980040631</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>59.8814148436764</v>
+        <v>59.6884656847209</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>59.8814148436764</v>
+        <v>59.6884656847209</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>-0.0132420980042232</v>
+        <v>-0.0200678227367567</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>-0.0927985272076267</v>
+        <v>-0.0912283087982954</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>-0.0131548071539224</v>
+        <v>-0.0198678041954651</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>1.01183705855629</v>
+        <v>1.00827589581045</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>0.995449729380049</v>
+        <v>0.999282493820236</v>
       </c>
     </row>
     <row r="14">
@@ -2174,46 +2232,46 @@
         <v>57.247</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-5.52948692025612</v>
+        <v>0.920549079992476</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>63.2366242346355</v>
+        <v>61.9103005795985</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>59.4907030108984</v>
+        <v>59.0492297928258</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>59.7449009679887</v>
+        <v>59.0357137085171</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>62.7764869202561</v>
+        <v>62.1878846486576</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>62.7764869202561</v>
+        <v>62.1878846486576</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>62.9168563894588</v>
+        <v>61.5577372213206</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>62.9168563894588</v>
+        <v>61.5577372213206</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>0.0494479276618754</v>
+        <v>0.0308367538855221</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>0.00696164018644696</v>
+        <v>-0.00957758114417007</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>0.0506908788596021</v>
+        <v>0.0313171316293053</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>0.994943312533727</v>
+        <v>0.994305255264839</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.05759140849172</v>
+        <v>1.04248162824978</v>
       </c>
     </row>
     <row r="15">
@@ -2233,46 +2291,46 @@
         <v>72.403</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2.96163120689993</v>
+        <v>1.03743941231241</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.775212465508573</v>
+        <v>0.270480950306479</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>65.535139678391</v>
+        <v>62.6180894370698</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>58.8584187515808</v>
+        <v>58.4080673021836</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>58.7914050689212</v>
+        <v>58.055149406732</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>69.4413687931001</v>
+        <v>69.7900996826568</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>68.563297181246</v>
+        <v>64.557981583904</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>64.7011935210751</v>
+        <v>61.9005237257192</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>64.7011935210751</v>
+        <v>61.9005237257192</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>0.027965533421342</v>
+        <v>0.00555308948366181</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>0.0526164253752008</v>
+        <v>0.00508929772520417</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>0.0283602397515081</v>
+        <v>0.00556853646465472</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>0.987274824446725</v>
+        <v>0.988540600363226</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>1.09926829319276</v>
+        <v>1.05979407614134</v>
       </c>
     </row>
     <row r="16">
@@ -2280,58 +2338,58 @@
         <v>66</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>60.698</v>
+        <v>57.665</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>60.698</v>
+        <v>57.665</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>60.698</v>
+        <v>57.665</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>60.698</v>
+        <v>57.665</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1.79630719844785</v>
+        <v>1.02427700655566</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>61.1473017457996</v>
+        <v>58.3270618484548</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>58.2649147189509</v>
+        <v>57.8160498202384</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>57.811624889503</v>
+        <v>57.0906602101483</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>58.9016928015522</v>
+        <v>56.298247086411</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>58.9016928015522</v>
+        <v>56.298247086411</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>60.8055828899521</v>
+        <v>58.2226068220825</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>60.8055828899521</v>
+        <v>58.2226068220825</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>-0.0620980397349511</v>
+        <v>-0.0612549278044888</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>0.00207547416507992</v>
+        <v>-0.0439383754406074</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>-0.0602092545611864</v>
+        <v>-0.0594165716583185</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>0.994411546444549</v>
+        <v>0.998209149868655</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.04360545592929</v>
+        <v>1.00703190555405</v>
       </c>
     </row>
     <row r="17">
@@ -2351,46 +2409,46 @@
         <v>48.993</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.695619968273469</v>
+        <v>1.01912967508285</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>56.855648775458</v>
+        <v>55.735951531604</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>57.7228869627417</v>
+        <v>57.2852350572825</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>56.8587297668411</v>
+        <v>56.1915143261086</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>48.2973800317265</v>
+        <v>48.0733720132496</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>56.855648775458</v>
+        <v>55.735951531604</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>56.6457514678616</v>
+        <v>55.4763383592418</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>56.6457514678616</v>
+        <v>55.4763383592418</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.0708646200970558</v>
+        <v>-0.0483171187099006</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>-0.0540345177925695</v>
+        <v>-0.070568530739723</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>-0.0684119981156848</v>
+        <v>-0.0471684215588769</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>0.996308241799766</v>
+        <v>0.995342087732816</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>0.981339542223947</v>
+        <v>0.968422985499983</v>
       </c>
     </row>
     <row r="18">
@@ -2410,46 +2468,46 @@
         <v>61.35</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>-4.76713119841544</v>
+        <v>0.92792925813889</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>53.9700155189781</v>
+        <v>54.1352032873481</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>57.2454295189876</v>
+        <v>56.8267320968997</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>55.9913393776029</v>
+        <v>55.4030178963369</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>66.1171311984154</v>
+        <v>66.1149537660308</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>53.9700155189781</v>
+        <v>54.1352032873481</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>53.3905440781326</v>
+        <v>53.4117535612821</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>53.3905440781326</v>
+        <v>53.4117535612821</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.0591833354098053</v>
+        <v>-0.0379257680852495</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>-0.151411129830737</v>
+        <v>-0.132330784524306</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>-0.0574660465326482</v>
+        <v>-0.0372155924313217</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>0.989263085524929</v>
+        <v>0.986636242553188</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>0.932660380518651</v>
+        <v>0.939905421100155</v>
       </c>
     </row>
     <row r="19">
@@ -2469,46 +2527,46 @@
         <v>50.972</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2.20550350088379</v>
+        <v>1.02681962658689</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>50.0390847002152</v>
+        <v>50.7443799709614</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>56.8450943998562</v>
+        <v>56.4506817204701</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>55.2680579934989</v>
+        <v>54.7681992485847</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>48.7664964991162</v>
+        <v>49.6406561388284</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>48.7664964991162</v>
+        <v>49.6406561388284</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>50.2524987391664</v>
+        <v>50.8168008535157</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>50.2524987391664</v>
+        <v>50.8168008535157</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.060573381242159</v>
+        <v>-0.0498038005209136</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>-0.22331419245307</v>
+        <v>-0.179057012850414</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>-0.0587753017533209</v>
+        <v>-0.0485839264720851</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>1.00426494689561</v>
+        <v>1.00142717050826</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>0.884025249139063</v>
+        <v>0.900198178387783</v>
       </c>
     </row>
     <row r="20">
@@ -2528,46 +2586,46 @@
         <v>50.491</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.984013560544951</v>
+        <v>1.01284460011627</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>49.2501938748498</v>
+        <v>49.7007713840009</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>56.5323864837647</v>
+        <v>56.165542503868</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>54.7373832669464</v>
+        <v>54.3237476375584</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>49.506986439455</v>
+        <v>49.8506878490578</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>49.506986439455</v>
+        <v>49.8506878490578</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>49.7768928951175</v>
+        <v>50.1331928669528</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>49.7768928951175</v>
+        <v>50.1331928669528</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>-0.00950939359527263</v>
+        <v>-0.0135437043820232</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>-0.181376272879328</v>
+        <v>-0.138939398228071</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>-0.0094643222920614</v>
+        <v>-0.0134524010776175</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>1.0106943542518</v>
+        <v>1.00870049842106</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>0.880502239356421</v>
+        <v>0.892596966609914</v>
       </c>
     </row>
     <row r="21">
@@ -2587,46 +2645,46 @@
         <v>53.162</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1.83489779755628</v>
+        <v>1.0385081439211</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>50.7315204970227</v>
+        <v>50.4722507486255</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>56.3127615254429</v>
+        <v>55.9755167569791</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>54.415305042891</v>
+        <v>54.080714602416</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>51.3271022024437</v>
+        <v>51.190739630867</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>51.3271022024437</v>
+        <v>51.190739630867</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>50.9740925229199</v>
+        <v>50.8265965160125</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>50.9740925229199</v>
+        <v>50.8265965160125</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>0.0237666356469804</v>
+        <v>0.0137364500552421</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>-0.100125054359275</v>
+        <v>-0.0838148655940394</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>0.0240513129319861</v>
+        <v>0.0138312285614823</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>1.00478148542604</v>
+        <v>1.00702060562252</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>0.905196107278261</v>
+        <v>0.908014779688039</v>
       </c>
     </row>
     <row r="22">
@@ -2646,46 +2704,46 @@
         <v>47.773</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-3.96217924733725</v>
+        <v>0.935364279260359</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>52.7840450725498</v>
+        <v>52.4421773290303</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>56.1872844045924</v>
+        <v>55.8808600055298</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>54.2916611821404</v>
+        <v>54.0277863833725</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>51.7351792473373</v>
+        <v>51.0742189532581</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>51.7351792473373</v>
+        <v>51.0742189532581</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>52.7870673344179</v>
+        <v>52.5097112809051</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>52.7870673344179</v>
+        <v>52.5097112809051</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>0.0349487099549879</v>
+        <v>0.0325783582276755</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>-0.0113030641311979</v>
+        <v>-0.0168884603150525</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>0.0355665931803064</v>
+        <v>0.0331148430204711</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>1.00005725710987</v>
+        <v>1.00128777932791</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>0.939484224834746</v>
+        <v>0.939672569028265</v>
       </c>
     </row>
     <row r="23">
@@ -2705,46 +2763,46 @@
         <v>56.927</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.576191359446505</v>
+        <v>1.00400941351935</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>55.5166580179783</v>
+        <v>55.5698661253937</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>56.1539039638384</v>
+        <v>55.8788372895429</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>54.3408485313006</v>
+        <v>54.1391993457855</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>56.3508086405535</v>
+        <v>56.6996675862371</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>56.3508086405535</v>
+        <v>56.6996675862371</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>55.2364560893482</v>
+        <v>55.2772227912564</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>55.2364560893482</v>
+        <v>55.2772227912564</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>0.0453569478299985</v>
+        <v>0.0513628099842294</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>0.0991782990941579</v>
+        <v>0.08777455217219</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>0.0464013039294806</v>
+        <v>0.0527047558030989</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>0.99495283148097</v>
+        <v>0.99473377651339</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>0.983661903986568</v>
+        <v>0.989233589540005</v>
       </c>
     </row>
     <row r="24">
@@ -2764,46 +2822,46 @@
         <v>57.208</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.698972171051361</v>
+        <v>1.01011140730582</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>56.5833708184007</v>
+        <v>56.8012904151935</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>56.2077864800825</v>
+        <v>55.9637094983832</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>54.5244815273032</v>
+        <v>54.3744220178619</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>56.5090278289486</v>
+        <v>56.6353370392933</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>56.5090278289486</v>
+        <v>56.6353370392933</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>56.068518902035</v>
+        <v>56.2016600955088</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>56.068518902035</v>
+        <v>56.2016600955088</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>0.0149513229355576</v>
+        <v>0.0165853562745113</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>0.126396519368421</v>
+        <v>0.121046892917053</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>0.01506365309427</v>
+        <v>0.0167236568259466</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>0.990901003087673</v>
+        <v>0.989443368006225</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>0.997522272504062</v>
+        <v>1.00425187320959</v>
       </c>
     </row>
     <row r="25">
@@ -2823,46 +2881,46 @@
         <v>57.825</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>2.91978869031064</v>
+        <v>1.05450224308904</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>54.7975195069813</v>
+        <v>54.7112976856287</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>56.3442212956492</v>
+        <v>56.1302505403512</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>54.8142244076262</v>
+        <v>54.7057252690109</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>54.9052113096894</v>
+        <v>54.8362987172113</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>54.9052113096894</v>
+        <v>54.8362987172113</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>54.8854258286948</v>
+        <v>54.8263578923915</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>54.8854258286948</v>
+        <v>54.8263578923915</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>-0.0213266489561605</v>
+        <v>-0.0247752337730522</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.0767317888791494</v>
+        <v>0.0786942595127134</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>-0.0211008440477505</v>
+        <v>-0.0244708466045315</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>1.00160420257166</v>
+        <v>1.00210304291125</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>0.974109226582443</v>
+        <v>0.976770232888551</v>
       </c>
     </row>
     <row r="26">
@@ -2882,46 +2940,46 @@
         <v>50.34</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-2.88225286645204</v>
+        <v>0.949856177339019</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>53.31040714041</v>
+        <v>53.1261017032144</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>56.5586860287062</v>
+        <v>56.3736540909603</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>55.1916641412558</v>
+        <v>55.1166845437488</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>53.222252866452</v>
+        <v>52.9974970958502</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>53.222252866452</v>
+        <v>52.9974970958502</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>53.9837264577365</v>
+        <v>53.8368911403838</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>53.9837264577365</v>
+        <v>53.8368911403838</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>-0.0165652064196517</v>
+        <v>-0.0182121206504598</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0.0226695511561097</v>
+        <v>0.0252749410938273</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>-0.0164287578595574</v>
+        <v>-0.0180472821840502</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>1.0126301664805</v>
+        <v>1.01337928841721</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>0.954472783019344</v>
+        <v>0.955000913254917</v>
       </c>
     </row>
     <row r="27">
@@ -2941,46 +2999,46 @@
         <v>53.219</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-1.32639549357486</v>
+        <v>0.976203955015673</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>0.957751632980441</v>
+        <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>55.4872850288403</v>
+        <v>55.3987083573923</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>56.84575891618</v>
+        <v>56.6883051058345</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>55.6388426316886</v>
+        <v>55.5915281538331</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>54.5453954935749</v>
+        <v>54.5162716526236</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>54.5851887883526</v>
+        <v>54.5162716526236</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>55.8694372868489</v>
+        <v>55.7808811331892</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>55.8694372868489</v>
+        <v>55.7808811331892</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.0343348523382903</v>
+        <v>0.0354722375479484</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.0114594824200316</v>
+        <v>0.00911149866980132</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.0349310978112771</v>
+        <v>0.0361088828055895</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>1.00688720411911</v>
+        <v>1.0068985863954</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>0.982825075292413</v>
+        <v>0.983992748222916</v>
       </c>
     </row>
     <row r="28">
@@ -3000,46 +3058,46 @@
         <v>61.631</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.457706314554155</v>
+        <v>1.00771744972773</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>0.900699928724892</v>
+        <v>0.931043705967028</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>60.2853287517342</v>
+        <v>60.2087790632978</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>57.1979329242706</v>
+        <v>57.0664784424758</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>56.127954726047</v>
+        <v>56.1038884737814</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>61.1732936854458</v>
+        <v>61.1590084270663</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>61.0851187042385</v>
+        <v>61.0934841316595</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>59.7988473248408</v>
+        <v>59.7238276340613</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>59.7988473248408</v>
+        <v>59.7238276340613</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>0.0679688936763011</v>
+        <v>0.0682998849650126</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>0.0665316026864122</v>
+        <v>0.0626701690406828</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>0.070332013866852</v>
+        <v>0.0706863430761768</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>0.991930351265118</v>
+        <v>0.991945503018311</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>1.04547217473774</v>
+        <v>1.04656585203981</v>
       </c>
     </row>
     <row r="29">
@@ -3059,46 +3117,46 @@
         <v>66.129</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>3.68903689746634</v>
+        <v>1.06330275452209</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>61.9574340438589</v>
+        <v>61.8646788542913</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>57.6062881628481</v>
+        <v>57.4990914374782</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>56.625927002237</v>
+        <v>56.6220215956058</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>62.4399631025337</v>
+        <v>62.1920706203025</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>62.4399631025337</v>
+        <v>62.1920706203025</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>61.200171187738</v>
+        <v>61.0956067564659</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>61.200171187738</v>
+        <v>61.0956067564659</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>0.0231636014331528</v>
+        <v>0.0227088974607901</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>0.115053227039768</v>
+        <v>0.114347352351566</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>0.0234339611144154</v>
+        <v>0.0229687074112155</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>0.987777691768435</v>
+        <v>0.987568478297014</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>1.06238699175913</v>
+        <v>1.06254908084762</v>
       </c>
     </row>
     <row r="30">
@@ -3118,46 +3176,46 @@
         <v>57.183</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-1.65263984164623</v>
+        <v>0.970769757213945</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>59.1203387771105</v>
+        <v>59.0399085535178</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>58.0643342328951</v>
+        <v>57.979578305991</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>57.1244718580553</v>
+        <v>57.1391315896073</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>58.8356398416462</v>
+        <v>58.9048016535991</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>58.8356398416462</v>
+        <v>58.9048016535991</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>59.2105231681156</v>
+        <v>59.1412268979363</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>59.2105231681156</v>
+        <v>59.1412268979363</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>-0.0330507043882659</v>
+        <v>-0.0325117012171616</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0.0968217100475841</v>
+        <v>0.0985260412552615</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>-0.0325104976180373</v>
+        <v>-0.0319888771433269</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>1.00152543765598</v>
+        <v>1.0017160992776</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>1.01973998238959</v>
+        <v>1.02003547845441</v>
       </c>
     </row>
     <row r="31">
@@ -3177,46 +3235,46 @@
         <v>54.274</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-2.4568498866362</v>
+        <v>0.959527885590254</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>57.4833284051815</v>
+        <v>57.3889216956623</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>58.5686017822313</v>
+        <v>58.5043063751531</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>57.6443718718002</v>
+        <v>57.6762727712105</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>56.7308498866362</v>
+        <v>56.5632336642445</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>56.7308498866362</v>
+        <v>56.5632336642445</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>57.7682192293999</v>
+        <v>57.6862898254512</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>57.7682192293999</v>
+        <v>57.6862898254512</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>-0.0246604981724557</v>
+        <v>-0.0249087259264401</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>0.033986058116213</v>
+        <v>0.0341588130835071</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>-0.0243589122599129</v>
+        <v>-0.0246010634002574</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>1.00495605999378</v>
+        <v>1.00518162950274</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>0.986334272486009</v>
+        <v>0.986017840388424</v>
       </c>
     </row>
     <row r="32">
@@ -3236,46 +3294,46 @@
         <v>58.253</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-0.52253730268102</v>
+        <v>0.992150233663501</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>57.7912724970372</v>
+        <v>57.7841191736944</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>59.1161035246823</v>
+        <v>59.0702212366956</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>58.2149654616878</v>
+        <v>58.2633278061602</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>58.775537302681</v>
+        <v>58.7138903197166</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>58.775537302681</v>
+        <v>58.7138903197166</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>57.9133824676443</v>
+        <v>57.9123062432034</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>57.9133824676443</v>
+        <v>57.9123062432034</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>0.00250970443542928</v>
+        <v>0.00391037111937579</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>-0.0315301204211226</v>
+        <v>-0.0303316358415169</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>0.00251285637987064</v>
+        <v>0.00391802659585361</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>1.00211294829359</v>
+        <v>1.00221837887887</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>0.979654933506639</v>
+        <v>0.980397652670837</v>
       </c>
     </row>
     <row r="33">
@@ -3295,46 +3353,46 @@
         <v>61.528</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>4.15639462142118</v>
+        <v>1.06711601497782</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>58.0823039238782</v>
+        <v>58.2709606648425</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>59.7027035791387</v>
+        <v>59.6730553119052</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>58.8610234360087</v>
+        <v>58.9246141646662</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>57.3716053785788</v>
+        <v>57.658210669136</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>57.3716053785788</v>
+        <v>57.658210669136</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>57.9611136801954</v>
+        <v>58.0976357330264</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>57.9611136801954</v>
+        <v>58.0976357330264</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>0.000823843327697083</v>
+        <v>0.00319506491126918</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>-0.0529256282242483</v>
+        <v>-0.049070157129134</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>0.000824182779823435</v>
+        <v>0.00320017457161237</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>0.997913473889714</v>
+        <v>0.997025535020556</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.970828960925786</v>
+        <v>0.97359914670626</v>
       </c>
     </row>
     <row r="34">
@@ -3354,46 +3412,46 @@
         <v>58.355</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.0292933390569257</v>
+        <v>0.999910362347738</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>58.0643575665634</v>
+        <v>58.0916886747991</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>60.3240532106024</v>
+        <v>60.3083183152455</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>59.6101194622582</v>
+        <v>59.686702129506</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>58.3257066609431</v>
+        <v>58.3602312741169</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>58.3257066609431</v>
+        <v>58.3602312741169</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>57.947118766408</v>
+        <v>57.9543976358865</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>57.947118766408</v>
+        <v>57.9543976358865</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>-0.000241482655029098</v>
+        <v>-0.0024685163321614</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>-0.0213374976964895</v>
+        <v>-0.0200677145926991</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>-0.000241453500439581</v>
+        <v>-0.00246547205118797</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>0.997980881816853</v>
+        <v>0.997636649199833</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.960597235800849</v>
+        <v>0.960968557155673</v>
       </c>
     </row>
     <row r="35">
@@ -3413,46 +3471,46 @@
         <v>54.485</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>-3.28045636516695</v>
+        <v>0.948572893367717</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>57.2570099931321</v>
+        <v>56.9636065955074</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>60.9743467476998</v>
+        <v>60.9702606832784</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>60.4823801176445</v>
+        <v>60.5698299659796</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>57.7654563651669</v>
+        <v>57.4389173261761</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>57.7654563651669</v>
+        <v>57.4389173261761</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>57.308603714868</v>
+        <v>57.102148597788</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>57.308603714868</v>
+        <v>57.102148597788</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>-0.0110800847060711</v>
+        <v>-0.0148147089976633</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.00795620015058329</v>
+        <v>-0.0101261708705944</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>-0.0110189266547295</v>
+        <v>-0.0147055111063862</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>1.00090109004543</v>
+        <v>1.00243211430176</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.93988056898748</v>
+        <v>0.936557396308604</v>
       </c>
     </row>
     <row r="36">
@@ -3472,46 +3530,46 @@
         <v>53.389</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>-1.98879546819512</v>
+        <v>0.967708693132723</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>56.2714683703754</v>
+        <v>56.1617126904299</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>61.6465295524641</v>
+        <v>61.6519152981651</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>61.4915099153692</v>
+        <v>61.58760358511</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>55.3777954681951</v>
+        <v>55.1705284646829</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>55.3777954681951</v>
+        <v>55.1705284646829</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>56.5738169002511</v>
+        <v>56.5211445148424</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>56.5738169002511</v>
+        <v>56.5211445148424</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>-0.0129044852991878</v>
+        <v>-0.0102269372937026</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>-0.0231305012816612</v>
+        <v>-0.0240218671748068</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>-0.0128215794311232</v>
+        <v>-0.0101748199886139</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>1.00537303430374</v>
+        <v>1.00639994414689</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.917712924165571</v>
+        <v>0.916778404068894</v>
       </c>
     </row>
     <row r="37">
@@ -3531,46 +3589,46 @@
         <v>62.628</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>4.85377970055284</v>
+        <v>1.07415188362687</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>57.1989754056247</v>
+        <v>57.6484337399347</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>62.3315414304389</v>
+        <v>62.3441079524687</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>62.6376287498717</v>
+        <v>62.7379743347211</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>57.7742202994472</v>
+        <v>58.3046038038278</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>57.7742202994472</v>
+        <v>58.3046038038278</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>57.6137719933715</v>
+        <v>57.9718352337997</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>57.6137719933715</v>
+        <v>57.9718352337997</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>0.0182153569880846</v>
+        <v>0.0253424858444698</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>-0.005992667579516</v>
+        <v>-0.0021653290644168</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>0.0183822685139665</v>
+        <v>0.0256663365791598</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>1.00725181849509</v>
+        <v>1.00560989211474</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.924311683478381</v>
+        <v>0.929868709934828</v>
       </c>
     </row>
     <row r="38">
@@ -3590,46 +3648,46 @@
         <v>65.51</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.36803703026654</v>
+        <v>1.02315053800393</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>59.5288519063965</v>
+        <v>60.1076048628604</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>63.0164042283658</v>
+        <v>63.0336135719811</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>63.8902879433553</v>
+        <v>63.9868081870347</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>64.1419629697335</v>
+        <v>64.0277237480653</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>59.5288519063965</v>
+        <v>60.1076048628604</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>59.8949019719184</v>
+        <v>60.4290330820978</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>59.8949019719184</v>
+        <v>60.4290330820978</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.0388297562865987</v>
+        <v>0.0415123764306539</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>0.0336131156643382</v>
+        <v>0.0426997009227641</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>0.0395934843288746</v>
+        <v>0.0423860627904602</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1.00614912019633</v>
+        <v>1.00534754662028</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>0.950465243222458</v>
+        <v>0.958679499043648</v>
       </c>
     </row>
     <row r="39">
@@ -3649,46 +3707,46 @@
         <v>54.322</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-3.87946995381259</v>
+        <v>0.944794708199529</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>62.7476837754334</v>
+        <v>63.1963187988425</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>63.6852914672788</v>
+        <v>63.7046823924017</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>65.1947217757713</v>
+        <v>65.2778042616183</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>58.2014699538126</v>
+        <v>57.4960883338562</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>62.7476837754334</v>
+        <v>63.1963187988425</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>63.1537798724184</v>
+        <v>63.6640990744683</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>63.1537798724184</v>
+        <v>63.6640990744683</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>0.0529813099506935</v>
+        <v>0.0521511402737783</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.101994740381956</v>
+        <v>0.114915999446902</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>0.0544099379614629</v>
+        <v>0.0535349620434182</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>1.00647188983801</v>
+        <v>1.0074020177839</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.99165409182223</v>
+        <v>0.999362946075402</v>
       </c>
     </row>
     <row r="40">
@@ -3708,46 +3766,46 @@
         <v>64.351</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>-3.23990003241015</v>
+        <v>0.94417006208405</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>67.3672726936465</v>
+        <v>67.7638697558548</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>64.3201969480114</v>
+        <v>64.3397358939862</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>66.4743573468862</v>
+        <v>66.5352656614184</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>67.5909000324101</v>
+        <v>68.156153837328</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>67.5909000324101</v>
+        <v>68.156153837328</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>67.4615789614256</v>
+        <v>67.8447698508065</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>67.4615789614256</v>
+        <v>67.8447698508065</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>0.0659855327837447</v>
+        <v>0.0636014894207722</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0.192452315536203</v>
+        <v>0.200343171270894</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>0.068211263010856</v>
+        <v>0.0656676343043507</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>1.00139988252468</v>
+        <v>1.00119385293731</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>1.04883974493973</v>
+        <v>1.05447697147212</v>
       </c>
     </row>
     <row r="41">
@@ -3767,46 +3825,46 @@
         <v>77.575</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>5.65816799455129</v>
+        <v>1.0793726328099</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>72.3490223562767</v>
+        <v>72.1207493973095</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>64.902528466589</v>
+        <v>64.9208778297449</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>67.6403865664647</v>
+        <v>67.6730880620675</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>71.9168320054487</v>
+        <v>71.8704529297275</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>71.9168320054487</v>
+        <v>71.8704529297275</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>71.8149122904208</v>
+        <v>71.6419708807077</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>71.8149122904208</v>
+        <v>71.6419708807077</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.0625339113054402</v>
+        <v>0.0544587883989465</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.246488639880811</v>
+        <v>0.235806501411875</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0645305579266739</v>
+        <v>0.0559689573455908</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>0.992617591109583</v>
+        <v>0.993361431757119</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>1.10650407599128</v>
+        <v>1.10352745180971</v>
       </c>
     </row>
     <row r="42">
@@ -3826,46 +3884,46 @@
         <v>77.807</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.97191488162449</v>
+        <v>1.04200002106925</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>74.9075675917337</v>
+        <v>74.1453054360598</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>65.4157380084654</v>
+        <v>65.4325972139022</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>68.6095840576993</v>
+        <v>68.6132715800778</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>75.8350851183755</v>
+        <v>74.6708238260478</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>75.8350851183755</v>
+        <v>74.6708238260478</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>74.3470562552328</v>
+        <v>73.7924299844307</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>74.3470562552328</v>
+        <v>73.7924299844307</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>0.0346519324958589</v>
+        <v>0.0295750638968236</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.241291893091173</v>
+        <v>0.221141994514089</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>0.0352593059582393</v>
+        <v>0.0300167496411257</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>0.992517293585665</v>
+        <v>0.995240758001417</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>1.13653164389297</v>
+        <v>1.12776250869578</v>
       </c>
     </row>
     <row r="43">
@@ -3885,46 +3943,46 @@
         <v>69.646</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>-4.15522277873157</v>
+        <v>0.941701485344581</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>74.3143198698728</v>
+        <v>74.4646514136876</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>65.8476614988057</v>
+        <v>65.8637265451203</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>69.3201066709772</v>
+        <v>69.2988031562999</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>73.8012227787316</v>
+        <v>73.9576193558998</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>73.8012227787316</v>
+        <v>73.9576193558998</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>74.0850611081834</v>
+        <v>74.2185787161687</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>74.0850611081834</v>
+        <v>74.2185787161687</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>-0.00353017155299795</v>
+        <v>0.0057583542335307</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.173089896722699</v>
+        <v>0.165783852989967</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>-0.00352394782316645</v>
+        <v>0.00577496542433775</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>0.996915012314035</v>
+        <v>0.996695442832978</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.12509783068799</v>
+        <v>1.12685058391473</v>
       </c>
     </row>
     <row r="44">
@@ -3944,46 +4002,46 @@
         <v>68.831</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>-4.07171375689483</v>
+        <v>0.926539497755063</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>72.9267934509517</v>
+        <v>73.983270873572</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>66.1926469547188</v>
+        <v>66.2088722136939</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>69.7462387619892</v>
+        <v>69.702957492814</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>72.9027137568948</v>
+        <v>74.2882523268273</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>72.9027137568948</v>
+        <v>74.2882523268273</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>73.2114458495793</v>
+        <v>73.9622414541335</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>73.2114458495793</v>
+        <v>73.9622414541335</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>-0.0118621346901986</v>
+        <v>-0.00345979347989248</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.0852317271056089</v>
+        <v>0.0901686543676046</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>-0.0117920569347759</v>
+        <v>-0.0034538152908512</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>1.00390326223268</v>
+        <v>0.999715754397039</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>1.10603593023953</v>
+        <v>1.11710468674674</v>
       </c>
     </row>
     <row r="45">
@@ -4003,46 +4061,46 @@
         <v>79.746</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>6.50686689420396</v>
+        <v>1.08771973088276</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>73.5972750723104</v>
+        <v>73.5168698229445</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>66.4500133691138</v>
+        <v>66.4676992929241</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>69.8846702669648</v>
+        <v>69.8223033726984</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>73.239133105796</v>
+        <v>73.3148418069796</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>73.239133105796</v>
+        <v>73.3148418069796</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>73.49077333671</v>
+        <v>73.4402499350255</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>73.49077333671</v>
+        <v>73.4402499350255</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>0.00380809269603768</v>
+        <v>-0.00708256280105702</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.0233358364278449</v>
+        <v>0.0251009154579538</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>0.0038153526936846</v>
+        <v>-0.00705754056185148</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>0.998552911972682</v>
+        <v>0.998957791754416</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>1.10595573440274</v>
+        <v>1.10490133878974</v>
       </c>
     </row>
     <row r="46">
@@ -4062,46 +4120,46 @@
         <v>76.223</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1.64088662164668</v>
+        <v>1.04640024766114</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>73.8090746549811</v>
+        <v>73.012278575068</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>66.6232735266509</v>
+        <v>66.6449224686833</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>69.7478734971078</v>
+        <v>69.6763360532014</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>74.5821133783533</v>
+        <v>72.8430637993155</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>74.5821133783533</v>
+        <v>72.8430637993155</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>73.5572736234123</v>
+        <v>72.7320336356489</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>73.5572736234123</v>
+        <v>72.7320336356489</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.000904470240992144</v>
+        <v>-0.00969023434399572</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>-0.0106229173231717</v>
+        <v>-0.0143699882088935</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.000904879397547909</v>
+        <v>-0.0096434353097008</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>0.996588481392758</v>
+        <v>0.996161673832286</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.10407774535407</v>
+        <v>1.0913364580749</v>
       </c>
     </row>
     <row r="47">
@@ -4121,46 +4179,46 @@
         <v>67.81</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>-4.01573463114651</v>
+        <v>0.942759246396773</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>72.2616465596496</v>
+        <v>70.9872570002078</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>66.7201834118258</v>
+        <v>66.7495358909147</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>69.3650930778166</v>
+        <v>69.302013483743</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>71.8257346311465</v>
+        <v>71.9271651369848</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>71.8257346311465</v>
+        <v>71.9271651369848</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>72.1564276865938</v>
+        <v>70.9423177388861</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>72.1564276865938</v>
+        <v>70.9423177388861</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>-0.0192279666689276</v>
+        <v>-0.0249147945857377</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>-0.0260326898937597</v>
+        <v>-0.0441434076744024</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>-0.0190442884546042</v>
+        <v>-0.0246069827461215</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.998543918135481</v>
+        <v>0.999366939036374</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>1.0814782573545</v>
+        <v>1.06281364794541</v>
       </c>
     </row>
     <row r="48">
@@ -4168,58 +4226,58 @@
         <v>98</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>66.2259600027535</v>
+        <v>60.425</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>66.2259600027535</v>
+        <v>60.425</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>66.2259600027535</v>
+        <v>60.425</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>66.2259600027535</v>
+        <v>60.425</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>-4.16616810297531</v>
+        <v>0.920429916259623</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>1</v>
+        <v>0.512904979973657</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>70.8888499057147</v>
+        <v>68.5704957821978</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>66.7534732840414</v>
+        <v>66.7944075478935</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>68.7897448338956</v>
+        <v>68.7521272524735</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>70.3921281057288</v>
+        <v>65.648670183984</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>70.3921281057288</v>
+        <v>67.0718768822594</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>70.5941776435659</v>
+        <v>68.6583473498603</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>70.5941776435659</v>
+        <v>68.6583473498603</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>-0.0218886976165605</v>
+        <v>-0.0327244029489378</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>-0.0357494402089921</v>
+        <v>-0.071710835150424</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>-0.0216508784194996</v>
+        <v>-0.0321947528896971</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>0.995843178969038</v>
+        <v>1.00128118612328</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>1.0575356482678</v>
+        <v>1.02790562668933</v>
       </c>
     </row>
     <row r="49">
@@ -4227,58 +4285,58 @@
         <v>99</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>76.7278610855513</v>
+        <v>74.973</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>76.7278610855513</v>
+        <v>74.973</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>76.7278610855513</v>
+        <v>74.973</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>76.7278610855513</v>
+        <v>74.973</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>6.96114135389173</v>
+        <v>1.09349910316104</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>68.3597361751522</v>
+        <v>68.3840454271175</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>66.739064372213</v>
+        <v>66.7956414461735</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>68.0875477979156</v>
+        <v>68.0925947058094</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>69.7667197316596</v>
+        <v>68.5624704979376</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>69.7667197316596</v>
+        <v>68.5624704979376</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>68.1489062900298</v>
+        <v>68.1053972843686</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>68.1489062900298</v>
+        <v>68.1053972843686</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>-0.0352525620156456</v>
+        <v>-0.00808625239047259</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>-0.0726875878990361</v>
+        <v>-0.0726420819016385</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>-0.034638428198462</v>
+        <v>-0.00805364659702701</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>0.996915876261105</v>
+        <v>0.995925246290878</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>1.02112468808304</v>
+        <v>1.01960840273164</v>
       </c>
     </row>
     <row r="50">
@@ -4286,58 +4344,58 @@
         <v>100</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>63.1680250265433</v>
+        <v>71.772</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>63.1680250265433</v>
+        <v>71.772</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>63.1680250265433</v>
+        <v>71.772</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>63.1680250265433</v>
+        <v>71.772</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.497967435472025</v>
+        <v>1.03726712268429</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>1</v>
+        <v>0.599401568615847</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>63.8565273097516</v>
+        <v>66.7755017499598</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>66.6951520645191</v>
+        <v>66.7695150106425</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>67.3322329188071</v>
+        <v>67.3809319383163</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>62.6700575910713</v>
+        <v>69.193362471824</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>62.6700575910713</v>
+        <v>68.2247712593398</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>64.0228251837975</v>
+        <v>66.4927558679657</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>64.0228251837975</v>
+        <v>66.4927558679657</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>-0.0624554461705341</v>
+        <v>-0.023963457880275</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>-0.129619383236359</v>
+        <v>-0.0857844536416895</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>-0.0605450818047237</v>
+        <v>-0.0236786140409608</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>1.00260424237039</v>
+        <v>0.995765724336257</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.959932216990278</v>
+        <v>0.995855007444151</v>
       </c>
     </row>
     <row r="51">
@@ -4357,46 +4415,46 @@
         <v>57.755</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>-3.22946582138786</v>
+        <v>0.947439920180495</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>60.4705486438964</v>
+        <v>62.1480723790958</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>66.6418240337381</v>
+        <v>66.7334099343457</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>66.6059270051688</v>
+        <v>66.6770044235203</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>60.9844658213879</v>
+        <v>60.9590104552458</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>60.9844658213879</v>
+        <v>60.9590104552458</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>61.3753273844577</v>
+        <v>62.7160926316845</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>61.3753273844577</v>
+        <v>62.7160926316845</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>-0.0422317430075583</v>
+        <v>-0.0584749319121856</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>-0.149412888744479</v>
+        <v>-0.115956531579353</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>-0.0413524050483457</v>
+        <v>-0.056798115629025</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.01496230414395</v>
+        <v>1.00913978874717</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.920973101717411</v>
+        <v>0.93980050912109</v>
       </c>
     </row>
     <row r="52">
@@ -4416,46 +4474,46 @@
         <v>52.019</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>-3.61694590614417</v>
+        <v>0.929475457093237</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>60.8623203039837</v>
+        <v>60.7215783569066</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>66.5966522686023</v>
+        <v>66.7056174454837</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>65.9674459889611</v>
+        <v>66.0448968315526</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>55.6359459061442</v>
+        <v>55.9659747904262</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>60.8623203039837</v>
+        <v>60.7215783569066</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>61.6124021243066</v>
+        <v>61.6533305914038</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>61.6124021243066</v>
+        <v>61.6533305914038</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>0.00385526319468826</v>
+        <v>-0.0170908231569803</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>-0.1272311091236</v>
+        <v>-0.102027168273673</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>0.00386270428121449</v>
+        <v>-0.0169456035235166</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>1.01232423963754</v>
+        <v>1.01534466428097</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.92515764720135</v>
+        <v>0.924259949198297</v>
       </c>
     </row>
     <row r="53">
@@ -4475,46 +4533,46 @@
         <v>70.2</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>6.45949793212904</v>
+        <v>1.0927647133772</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>1</v>
+        <v>0.94479850650331</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>63.90573149401</v>
+        <v>63.7050145797987</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>66.5736729089615</v>
+        <v>66.7008197725827</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>65.4474984962253</v>
+        <v>65.5201038627032</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>63.740502067871</v>
+        <v>64.2407273410634</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>63.740502067871</v>
+        <v>64.2111551965563</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>64.0333482574159</v>
+        <v>63.8715891714559</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>64.0333482574159</v>
+        <v>63.8715891714559</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>0.0385408307123125</v>
+        <v>0.0353473962656272</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>-0.0603906688553268</v>
+        <v>-0.062165529924666</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>0.0392931625717978</v>
+        <v>0.0359795417177573</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>1.00199695333145</v>
+        <v>1.00261477990007</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>0.961841903254767</v>
+        <v>0.957583270928707</v>
       </c>
     </row>
     <row r="54">
@@ -4534,46 +4592,46 @@
         <v>67.321</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>-0.469068589938004</v>
+        <v>1.01474970851465</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>67.2784019774082</v>
+        <v>66.6036868350842</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>66.5833381371875</v>
+        <v>66.7299591197385</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>65.0512675245779</v>
+        <v>65.1115036248887</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>67.790068589938</v>
+        <v>66.3424679358044</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>67.790068589938</v>
+        <v>66.3424679358044</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>66.6344729518251</v>
+        <v>66.09745009335</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>66.6344729518251</v>
+        <v>66.09745009335</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>0.0398180413470092</v>
+        <v>0.0342555210053571</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>0.0407924480141275</v>
+        <v>-0.00594509536348109</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>0.0406214068949295</v>
+        <v>0.0348489986043565</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>0.990428889410909</v>
+        <v>0.992399268482124</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>1.0007679821419</v>
+        <v>0.990521363496514</v>
       </c>
     </row>
     <row r="55">
@@ -4593,46 +4651,46 @@
         <v>64.595</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>-2.62225255955357</v>
+        <v>0.957052155896103</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>66.9244469383945</v>
+        <v>66.8193840645143</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>66.6343294038763</v>
+        <v>66.8024216506868</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>64.7754010894934</v>
+        <v>64.8214294826949</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>67.2172525595536</v>
+        <v>67.493709305235</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>67.2172525595536</v>
+        <v>67.493709305235</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>66.462477919367</v>
+        <v>66.4230899029743</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>66.462477919367</v>
+        <v>66.4230899029743</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>-0.00258450891732325</v>
+        <v>0.00491456592409731</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>0.0828859209669572</v>
+        <v>0.0591075928958154</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>-0.00258117194957808</v>
+        <v>0.00492666221109017</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>0.993097155969734</v>
+        <v>0.994069173682335</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>0.997420976754073</v>
+        <v>0.994321586877553</v>
       </c>
     </row>
     <row r="56">
@@ -4652,46 +4710,46 @@
         <v>61.524</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>-2.10133796842266</v>
+        <v>0.955898632690373</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>64.2601518651742</v>
+        <v>65.016766598837</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>66.736082366157</v>
+        <v>66.9273513471735</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>64.6302412117735</v>
+        <v>64.6583696222625</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>63.6253379684227</v>
+        <v>64.362473065623</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>63.6253379684227</v>
+        <v>64.362473065623</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>64.2683177505848</v>
+        <v>64.7825113977727</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>64.2683177505848</v>
+        <v>64.7825113977727</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>-0.0335707622853327</v>
+        <v>-0.0250090544419944</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>0.0431068345772294</v>
+        <v>0.0507544487273031</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>-0.0330135173630476</v>
+        <v>-0.0246989188187131</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1.00012707541413</v>
+        <v>0.996397003214422</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>0.963022033537532</v>
+        <v>0.967952714305474</v>
       </c>
     </row>
     <row r="57">
@@ -4711,46 +4769,46 @@
         <v>67.722</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>5.11665749405981</v>
+        <v>1.07646643689748</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>62.1024455162534</v>
+        <v>62.1982217405433</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>66.8983970081311</v>
+        <v>67.1143242457286</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>64.6383391695698</v>
+        <v>64.6441736288447</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>62.6053425059402</v>
+        <v>62.9113901546098</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>62.6053425059402</v>
+        <v>62.9113901546098</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>62.4846865381779</v>
+        <v>62.5943725247505</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>62.4846865381779</v>
+        <v>62.5943725247505</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>-0.0281452729861002</v>
+        <v>-0.0343603028012247</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>-0.0241852372456353</v>
+        <v>-0.0199966317305321</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>-0.0277528847001853</v>
+        <v>-0.0337766910514903</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1.00615500756447</v>
+        <v>1.00636916575943</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>0.934023673700033</v>
+        <v>0.932652950442755</v>
       </c>
     </row>
     <row r="58">
@@ -4770,46 +4828,46 @@
         <v>59.717</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>-1.38572317240865</v>
+        <v>0.992104684091785</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>61.7989606788694</v>
+        <v>61.3109186095921</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>67.1291290986512</v>
+        <v>67.3713133339558</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>64.8172217248175</v>
+        <v>64.7992116049114</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>61.1027231724087</v>
+        <v>60.1922367241593</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>61.1027231724087</v>
+        <v>60.1922367241593</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>61.9306759672269</v>
+        <v>61.5663317801837</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>61.9306759672269</v>
+        <v>61.5663317801837</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>-0.00890588142100927</v>
+        <v>-0.0165602191844207</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>-0.0705910435878886</v>
+        <v>-0.0685520894795036</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>-0.00886634152533616</v>
+        <v>-0.0164238525461745</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>1.00213135118958</v>
+        <v>1.00416586762006</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>0.922560396638174</v>
+        <v>0.913836004279786</v>
       </c>
     </row>
     <row r="59">
@@ -4829,46 +4887,46 @@
         <v>60.997</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>-1.91491501814997</v>
+        <v>0.96867587227818</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>62.0446575288382</v>
+        <v>61.911222451334</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>67.4334512475064</v>
+        <v>67.7036647656524</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>65.1742506561334</v>
+        <v>65.1351897355614</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>62.91191501815</v>
+        <v>62.9694635178062</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>62.91191501815</v>
+        <v>62.9694635178062</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>62.3179536368848</v>
+        <v>62.2258257926454</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>62.3179536368848</v>
+        <v>62.2258257926454</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.00623393473373453</v>
+        <v>0.0106549601306464</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>-0.0623588588964491</v>
+        <v>-0.0631898352886019</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.00625340614500769</v>
+        <v>0.0107119263628763</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>1.00440482902045</v>
+        <v>1.00508152365363</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>0.924140059332782</v>
+        <v>0.91909095331888</v>
       </c>
     </row>
     <row r="60">
@@ -4888,46 +4946,46 @@
         <v>62.056</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>-0.289261338830595</v>
+        <v>0.988591444906425</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>63.061387222171</v>
+        <v>63.4116677555026</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>67.8127695607815</v>
+        <v>68.1122377717342</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>65.6982152493723</v>
+        <v>65.6407793314898</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>62.3452613388306</v>
+        <v>62.7721394108098</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>62.3452613388306</v>
+        <v>62.7721394108098</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>63.2821910427103</v>
+        <v>63.5138277736434</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>63.2821910427103</v>
+        <v>63.5138277736434</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>0.0153543827839756</v>
+        <v>0.0204875231665361</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>-0.0153439010447022</v>
+        <v>-0.0195837363627265</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>0.0154728669597202</v>
+        <v>0.0206988330743894</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>1.00350141077235</v>
+        <v>1.00161106026315</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>0.933189891116151</v>
+        <v>0.932487756260461</v>
       </c>
     </row>
     <row r="61">
@@ -4947,46 +5005,46 @@
         <v>68.644</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3.11767352496986</v>
+        <v>1.04733532174737</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>65.3927875652057</v>
+        <v>65.4275767941949</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>68.2656641844185</v>
+        <v>68.5949327073371</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>66.3665931121992</v>
+        <v>66.293823072303</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>65.5263264750301</v>
+        <v>65.5415687551477</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>65.5263264750301</v>
+        <v>65.5415687551477</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>65.5559091374435</v>
+        <v>65.5911414609501</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>65.5559091374435</v>
+        <v>65.5911414609501</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>0.0352994057422899</v>
+        <v>0.0321830057192789</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.0491516044877496</v>
+        <v>0.0478760120970085</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>0.0359298257103418</v>
+        <v>0.0327064792049696</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>1.00249448873968</v>
+        <v>1.00249993465706</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>0.96030573965186</v>
+        <v>0.956209720924973</v>
       </c>
     </row>
     <row r="62">
@@ -5006,46 +5064,46 @@
         <v>67.255</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>-1.57072226088291</v>
+        <v>0.981691695499709</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>68.3136297940989</v>
+        <v>68.1104420869422</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>68.7872980717201</v>
+        <v>69.1463123661215</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>67.1400970827263</v>
+        <v>67.0578204380038</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>68.8257222608829</v>
+        <v>68.5092889226951</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>68.8257222608829</v>
+        <v>68.5092889226951</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>68.4026260748037</v>
+        <v>68.2548614575671</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>68.4026260748037</v>
+        <v>68.2548614575671</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>0.0425078636269833</v>
+        <v>0.0398080135493593</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>0.104503140107847</v>
+        <v>0.108639405402034</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>0.0434242614405946</v>
+        <v>0.0406109718063516</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>1.0013027602394</v>
+        <v>1.00212037047771</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.994407804817171</v>
+        <v>0.98710775921304</v>
       </c>
     </row>
     <row r="63">
@@ -5065,46 +5123,46 @@
         <v>68.767</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>-1.66573330241868</v>
+        <v>0.97598188956985</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>71.7904219268575</v>
+        <v>71.790439701387</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>69.3711220899211</v>
+        <v>69.7590311892779</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>67.9752386658798</v>
+        <v>67.8925096370093</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>70.4327333024187</v>
+        <v>70.4592992297306</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>70.4327333024187</v>
+        <v>70.4592992297306</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>71.3406456287544</v>
+        <v>71.3114569049975</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>71.3406456287544</v>
+        <v>71.3114569049975</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>0.0420550131163847</v>
+        <v>0.0438083387404195</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>0.144784792588717</v>
+        <v>0.146010615313135</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>0.042951853204259</v>
+        <v>0.0447820914460513</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>0.993734870390352</v>
+        <v>0.993328042029247</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>1.02839111548867</v>
+        <v>1.02225411805831</v>
       </c>
     </row>
     <row r="64">
@@ -5124,46 +5182,46 @@
         <v>77.802</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>1.65157980676543</v>
+        <v>1.02005761489572</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>0.814028956793087</v>
+        <v>0.83696958993803</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>73.5746076598601</v>
+        <v>73.4860434654854</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>70.0106111213742</v>
+        <v>70.4253454783442</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>68.8369574924771</v>
+        <v>68.7648862201601</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>76.1504201932346</v>
+        <v>76.2721623405102</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>75.6713936492975</v>
+        <v>75.8179402378335</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>73.3463774744765</v>
+        <v>73.1344626869162</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>73.3463774744765</v>
+        <v>73.1344626869162</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>0.0277268866039965</v>
+        <v>0.025242701029285</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>0.159036630463279</v>
+        <v>0.15147307681659</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>0.0281148541346197</v>
+        <v>0.0255639957594378</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>0.996897976181691</v>
+        <v>0.995215679576839</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>1.04764658242047</v>
+        <v>1.03846792926852</v>
       </c>
     </row>
     <row r="65">
@@ -5183,46 +5241,46 @@
         <v>65.9</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.12449725715489</v>
+        <v>1.01475233829397</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>0</v>
+        <v>0.110726589945484</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>71.6099892968922</v>
+        <v>71.1275848134228</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>70.6999035554399</v>
+        <v>71.137949202384</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>69.7024806665179</v>
+        <v>69.6547796862604</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>64.7755027428451</v>
+        <v>64.941954320394</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>71.6099892968922</v>
+        <v>70.4426710422669</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>72.0084864973699</v>
+        <v>71.3606050632032</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>72.0084864973699</v>
+        <v>71.3606050632032</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>-0.0184091364291904</v>
+        <v>-0.0245537341850156</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>0.0984286152816236</v>
+        <v>0.0879610184202688</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>-0.0182407233073248</v>
+        <v>-0.0242547433664312</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>1.00556482698001</v>
+        <v>1.0032760883192</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>1.01850897775135</v>
+        <v>1.00312991677882</v>
       </c>
     </row>
     <row r="66">
@@ -5242,46 +5300,46 @@
         <v>67.304</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>-1.8385737463979</v>
+        <v>0.979121967867891</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>69.8697976398193</v>
+        <v>69.4272179520362</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>71.436675770559</v>
+        <v>71.8929067021852</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>70.5832074727862</v>
+        <v>70.5772848042027</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>69.1425737463979</v>
+        <v>68.7391379304453</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>69.1425737463979</v>
+        <v>68.7391379304453</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>70.4338961188289</v>
+        <v>69.9509588855054</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>70.4338961188289</v>
+        <v>69.9509588855054</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>-0.0221093538383617</v>
+        <v>-0.019951558087078</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>0.0296957903605022</v>
+        <v>0.0248494743336738</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>-0.0218667334245194</v>
+        <v>-0.0197538428443712</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>1.00807356680661</v>
+        <v>1.00754374075353</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.985962677561441</v>
+        <v>0.972988325194247</v>
       </c>
     </row>
     <row r="67">
@@ -5301,46 +5359,46 @@
         <v>70.755</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>-1.08544768562742</v>
+        <v>0.984309358454825</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>70.5045250019088</v>
+        <v>70.5390108926394</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>72.2191729487603</v>
+        <v>72.685847769686</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>71.5000747392178</v>
+        <v>71.5514357996596</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>71.8404476856274</v>
+        <v>71.8828886388641</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>71.8404476856274</v>
+        <v>71.8828886388641</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>70.7118764733872</v>
+        <v>70.6967618915094</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>70.7118764733872</v>
+        <v>70.6967618915094</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>0.00393891660883534</v>
+        <v>0.0106053619943416</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>-0.00881361739616482</v>
+        <v>-0.00861986334547915</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>0.00394668433632273</v>
+        <v>0.0106617981781303</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>1.00294096685954</v>
+        <v>1.00223636533705</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>0.979128859915876</v>
+        <v>0.972634481962992</v>
       </c>
     </row>
     <row r="68">
@@ -5360,46 +5418,46 @@
         <v>72.93</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>2.90596322410385</v>
+        <v>1.03767483360712</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>71.0538176745379</v>
+        <v>71.1870599806136</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>73.0442064583079</v>
+        <v>73.510431091342</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>72.4668161251165</v>
+        <v>72.5870761639349</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>70.0240367758961</v>
+        <v>70.2821323578639</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>70.0240367758961</v>
+        <v>70.2821323578639</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>71.3124347573109</v>
+        <v>71.4667763277718</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>71.3124347573109</v>
+        <v>71.4667763277718</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.00845716987787462</v>
+        <v>0.0108329037966864</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>-0.0277306499270991</v>
+        <v>-0.0228030164969367</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.00849303276727076</v>
+        <v>0.010891792150878</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>1.00363973522095</v>
+        <v>1.0039293145023</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>0.976291457119389</v>
+        <v>0.972199118774983</v>
       </c>
     </row>
     <row r="69">
@@ -5419,46 +5477,46 @@
         <v>66.714</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>-0.124592614768912</v>
+        <v>0.99496973529098</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>0</v>
+        <v>0.0256394031393836</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>73.3612177918239</v>
+        <v>73.5875375523418</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>73.908350964176</v>
+        <v>74.3598135041521</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>73.4988671545184</v>
+        <v>73.6957066525285</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>66.8385926147689</v>
+        <v>67.0512857162328</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>73.3612177918239</v>
+        <v>73.4199519564953</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>73.3774176045397</v>
+        <v>73.5234576791806</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>73.3774176045397</v>
+        <v>73.5234576791806</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.0285455134817548</v>
+        <v>0.028371832433823</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.019010691291502</v>
+        <v>0.030308776306784</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.0289568411772272</v>
+        <v>0.0287781463931729</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>1.00022082257088</v>
+        <v>0.999129202100075</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>0.992816327888392</v>
+        <v>0.988752583074662</v>
       </c>
     </row>
     <row r="70">
@@ -5478,46 +5536,46 @@
         <v>75.119</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>-2.31387097410215</v>
+        <v>0.975928917089613</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>0.726693190019516</v>
+        <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>74.9826103474643</v>
+        <v>75.226089325542</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>74.8062935252877</v>
+        <v>75.225134158407</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>74.5994494547131</v>
+        <v>74.8773033019096</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>77.4328709741021</v>
+        <v>76.9717944458677</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>76.763198058615</v>
+        <v>76.9717944458677</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>74.6058146386275</v>
+        <v>74.7171997869384</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>74.6058146386275</v>
+        <v>74.7171997869384</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0166022221704535</v>
+        <v>0.0161058097351808</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.059231687435837</v>
+        <v>0.0681368915790599</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.0167408049259532</v>
+        <v>0.0162362074015439</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>0.994974892083768</v>
+        <v>0.993235198809798</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>0.997320026468196</v>
+        <v>0.993247810360842</v>
       </c>
     </row>
     <row r="71">
@@ -5537,46 +5595,46 @@
         <v>70.535</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>-1.00064464545627</v>
+        <v>0.986430951756604</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>72.1563222041037</v>
+        <v>72.4677421523481</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>75.732379242333</v>
+        <v>76.0969447909299</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>75.7710964061771</v>
+        <v>76.1304633750678</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>71.5356446454563</v>
+        <v>71.5052582995227</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>71.5356446454563</v>
+        <v>71.5052582995227</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>72.2772409092926</v>
+        <v>72.4654276816316</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>72.2772409092926</v>
+        <v>72.4654276816316</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>-0.0317091556509058</v>
+        <v>-0.0306007285702215</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.0221372209871213</v>
+        <v>0.0250176350769282</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>-0.0312116922871758</v>
+        <v>-0.0301372657397202</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>1.00167578808752</v>
+        <v>0.999968062055644</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>0.954377000067772</v>
+        <v>0.95227775412961</v>
       </c>
     </row>
     <row r="72">
@@ -5596,46 +5654,46 @@
         <v>73.632</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>4.35752371235709</v>
+        <v>1.05370109553723</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>69.1829825036717</v>
+        <v>69.5924577326419</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>76.6821762813357</v>
+        <v>76.9668888012235</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>77.0271601324063</v>
+        <v>77.464256590712</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>69.2744762876429</v>
+        <v>69.8793996816134</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>69.2744762876429</v>
+        <v>69.8793996816134</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>70.4964742245389</v>
+        <v>70.8700162157073</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>70.4964742245389</v>
+        <v>70.8700162157073</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>-0.0249465951706613</v>
+        <v>-0.0222621469319188</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>-0.0114420512432213</v>
+        <v>-0.00835017532241167</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>-0.0246380003214095</v>
+        <v>-0.0220161740151947</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>1.01898576316506</v>
+        <v>1.01835771468186</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>0.919333248523067</v>
+        <v>0.920785773200966</v>
       </c>
     </row>
     <row r="73">
@@ -5655,46 +5713,46 @@
         <v>71.538</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>-0.36329967741337</v>
+        <v>0.990611400070883</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>73.2525589279961</v>
+        <v>73.4998509557089</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>77.6486298491962</v>
+        <v>77.8237397847336</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>78.3598154980928</v>
+        <v>78.8646266421737</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>71.9012996774134</v>
+        <v>72.2160072000798</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>71.9012996774134</v>
+        <v>72.2160072000798</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>74.0088327311681</v>
+        <v>74.2140399028949</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>74.0088327311681</v>
+        <v>74.2140399028949</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>0.048621749745003</v>
+        <v>0.04610590766287</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.00860503336368801</v>
+        <v>0.00939267881997186</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>0.0498231797443083</v>
+        <v>0.0471853100330799</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>1.01032419637265</v>
+        <v>1.00971687612831</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>0.953124773417161</v>
+        <v>0.953616982532278</v>
       </c>
     </row>
     <row r="74">
@@ -5714,46 +5772,46 @@
         <v>79.132</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>-3.82625528220259</v>
+        <v>0.958655811367494</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>81.8705317697403</v>
+        <v>81.6295173359938</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>78.6200553403188</v>
+        <v>78.6518416562064</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>79.7224739487052</v>
+        <v>80.2795929382385</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>82.9582552822026</v>
+        <v>82.5447455298065</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>82.9582552822026</v>
+        <v>82.5447455298065</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>81.3506074329749</v>
+        <v>81.1790120905104</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>81.3506074329749</v>
+        <v>81.1790120905104</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>0.0945838532320961</v>
+        <v>0.089703392672099</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.090405725438661</v>
+        <v>0.0864835984485284</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>0.0992013308529718</v>
+        <v>0.0938497917203918</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.993649432518313</v>
+        <v>0.994481098747294</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.03473098665266</v>
+        <v>1.03213110311327</v>
       </c>
     </row>
     <row r="75">
@@ -5773,46 +5831,46 @@
         <v>86.477</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>-1.10761949008116</v>
+        <v>0.989319937910748</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>87.1651263785404</v>
+        <v>86.9081155393816</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>79.5811760677507</v>
+        <v>79.4320334975223</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>81.0362543506084</v>
+        <v>81.623931790482</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>87.5846194900812</v>
+        <v>87.4105501023488</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>87.5846194900812</v>
+        <v>87.4105501023488</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>85.9652303160166</v>
+        <v>85.797184609399</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>85.9652303160166</v>
+        <v>85.797184609399</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>0.0551746153065211</v>
+        <v>0.0553294505789794</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.189381736692222</v>
+        <v>0.183974032228705</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>0.056725118946944</v>
+        <v>0.0568887499362472</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>0.98623421874807</v>
+        <v>0.987217178475362</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.08022065724225</v>
+        <v>1.08013330178781</v>
       </c>
     </row>
     <row r="76">
@@ -5832,46 +5890,46 @@
         <v>91.623</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>5.88957299829868</v>
+        <v>1.06758228619692</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>85.9037973800311</v>
+        <v>86.1256759316116</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>80.5194267195026</v>
+        <v>80.147587455483</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>82.238454476835</v>
+        <v>82.8237452734375</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>85.7334270017013</v>
+        <v>85.8228927030921</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>85.7334270017013</v>
+        <v>85.8228927030921</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>85.530570668284</v>
+        <v>85.6725652161153</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>85.530570668284</v>
+        <v>85.6725652161153</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>-0.00506905213961959</v>
+        <v>-0.00145354402571565</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>0.2132602603055</v>
+        <v>0.20886899412233</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>-0.00505622617580048</v>
+        <v>-0.0014524881422513</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>0.995655294374288</v>
+        <v>0.994738958962063</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.06223521643092</v>
+        <v>1.06893504765444</v>
       </c>
     </row>
     <row r="77">
@@ -5891,46 +5949,46 @@
         <v>83.511</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>0.440190820347816</v>
+        <v>0.998530197459879</v>
       </c>
       <c r="G77" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>82.9842114195784</v>
+        <v>83.2933055611041</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>81.4272441357241</v>
+        <v>80.7867622497681</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>83.2991139261149</v>
+        <v>83.8340685531974</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>83.0708091796522</v>
+        <v>83.6339253559284</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>83.0708091796522</v>
+        <v>83.6339253559284</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>84.0142047237562</v>
+        <v>84.2434095816383</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>84.0142047237562</v>
+        <v>84.2434095816383</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>-0.0178879753110746</v>
+        <v>-0.0168223068970778</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>0.135191592994473</v>
+        <v>0.135141136257591</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>-0.0177289351945145</v>
+        <v>-0.0166816019909282</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1.01241191892479</v>
+        <v>1.01140672727699</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>1.03177020928917</v>
+        <v>1.0427872987555</v>
       </c>
     </row>
     <row r="78">
@@ -5950,46 +6008,46 @@
         <v>70.96</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>-5.91766712601674</v>
+        <v>0.9339617071481</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>84.181773534019</v>
+        <v>83.8828949116042</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>82.3003239067415</v>
+        <v>81.341363665837</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>84.2057471598023</v>
+        <v>84.6249325330027</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>76.8776671260167</v>
+        <v>75.9774190493098</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>84.181773534019</v>
+        <v>83.8828949116042</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>85.3271072673365</v>
+        <v>85.1012061171187</v>
       </c>
       <c r="N78" s="14" t="n">
-        <v>85.3271072673365</v>
+        <v>85.1012061171187</v>
       </c>
       <c r="O78" s="15" t="n">
-        <v>0.0155063030376089</v>
+        <v>0.010130866795524</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>0.0488810097409271</v>
+        <v>0.048315370261407</v>
       </c>
       <c r="Q78" s="17" t="n">
-        <v>0.0156271495742566</v>
+        <v>0.0101823577623494</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>1.01360548352969</v>
+        <v>1.01452395278916</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>1.03677729584667</v>
+        <v>1.04622300735856</v>
       </c>
     </row>
     <row r="79">
@@ -6009,46 +6067,46 @@
         <v>88.168</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>-1.70607282165586</v>
+        <v>0.990594817578208</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>88.9494123073555</v>
+        <v>88.2014472183073</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>83.1353888510331</v>
+        <v>81.8049769660904</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>84.9447271155191</v>
+        <v>85.1653674001077</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>89.8740728216559</v>
+        <v>89.0051092893378</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>89.8740728216559</v>
+        <v>89.0051092893378</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>88.8610429482922</v>
+        <v>88.3356493140698</v>
       </c>
       <c r="N79" s="14" t="n">
-        <v>88.8610429482922</v>
+        <v>88.3356493140698</v>
       </c>
       <c r="O79" s="15" t="n">
-        <v>0.0405816429829733</v>
+        <v>0.0373025472062487</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>0.0336858590575548</v>
+        <v>0.0295868065627958</v>
       </c>
       <c r="Q79" s="17" t="n">
-        <v>0.0414163305675364</v>
+        <v>0.0380070194598632</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>0.999006521158813</v>
+        <v>1.00152154074559</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>1.06887144182989</v>
+        <v>1.07983221302888</v>
       </c>
     </row>
     <row r="80">
@@ -6068,46 +6126,46 @@
         <v>99.067</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>7.55274738416218</v>
+        <v>1.08329753127412</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>91.3856911284478</v>
+        <v>91.5257552195274</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>83.9303376930946</v>
+        <v>82.1727758699575</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>85.5023068627583</v>
+        <v>85.4206931536601</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>91.5142526158378</v>
+        <v>91.4494837659995</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>91.5142526158378</v>
+        <v>91.4494837659995</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>90.2519495868754</v>
+        <v>90.3178165793879</v>
       </c>
       <c r="N80" s="14" t="n">
-        <v>90.2519495868754</v>
+        <v>90.3178165793879</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>0.0155313646286198</v>
+        <v>0.0221909896489051</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>0.0552010688307278</v>
+        <v>0.0542209907168592</v>
       </c>
       <c r="Q80" s="17" t="n">
-        <v>0.0156526031254507</v>
+        <v>0.0224390410973334</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>0.987593883379632</v>
+        <v>0.986802199695132</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>1.0753197481094</v>
+        <v>1.09912091472144</v>
       </c>
     </row>
     <row r="81">
@@ -6127,46 +6185,46 @@
         <v>89.526</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1.42077970582993</v>
+        <v>1.00177705603903</v>
       </c>
       <c r="G81" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>87.5811844911402</v>
+        <v>88.3608383271726</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>84.6872808349031</v>
+        <v>82.4444341795698</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>85.8893861995436</v>
+        <v>85.3754285022535</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>88.1052202941701</v>
+        <v>89.3671894962146</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>88.1052202941701</v>
+        <v>89.3671894962146</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>87.5050692637119</v>
+        <v>87.9705313971834</v>
       </c>
       <c r="N81" s="14" t="n">
-        <v>87.5050692637119</v>
+        <v>87.9705313971834</v>
       </c>
       <c r="O81" s="15" t="n">
-        <v>-0.0309084729224553</v>
+        <v>-0.0263328573631497</v>
       </c>
       <c r="P81" s="16" t="n">
-        <v>0.0415508847751864</v>
+        <v>0.0442422954395409</v>
       </c>
       <c r="Q81" s="17" t="n">
-        <v>-0.0304356895971473</v>
+        <v>-0.0259891710307375</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>0.999130918040552</v>
+        <v>0.995582806395023</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>1.03327286460292</v>
+        <v>1.06702814171272</v>
       </c>
     </row>
     <row r="82">
@@ -6186,46 +6244,46 @@
         <v>69.779</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>-7.50541299572493</v>
+        <v>0.916194654780322</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>82.2955838506696</v>
+        <v>81.6982628303047</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>85.4130686252626</v>
+        <v>82.6254236394936</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>86.146924652664</v>
+        <v>85.0442361075431</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>77.2844129957249</v>
+        <v>76.1617628261879</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>82.2955838506696</v>
+        <v>81.6982628303047</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>83.4861448027766</v>
+        <v>82.9461042230634</v>
       </c>
       <c r="N82" s="14" t="n">
-        <v>83.4861448027766</v>
+        <v>82.9461042230634</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>-0.0470160385447038</v>
+        <v>-0.0588108377403786</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>-0.0215753530562334</v>
+        <v>-0.0253239876658071</v>
       </c>
       <c r="Q82" s="17" t="n">
-        <v>-0.0459279044602948</v>
+        <v>-0.0571148894330858</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>1.01446688748533</v>
+        <v>1.01527378122287</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>0.977439941527683</v>
+        <v>1.00388113693636</v>
       </c>
     </row>
     <row r="83">
@@ -6245,46 +6303,46 @@
         <v>78.684</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>-2.56419121559726</v>
+        <v>0.995739069281401</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>82.122136055471</v>
+        <v>80.7426544991856</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>86.1166876251391</v>
+        <v>82.7255427163681</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>86.3269609193818</v>
+        <v>84.4617374361543</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>81.2481912155973</v>
+        <v>79.0207017354297</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>81.2481912155973</v>
+        <v>79.0207017354297</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>82.9805933791714</v>
+        <v>81.9284793457735</v>
       </c>
       <c r="N83" s="14" t="n">
-        <v>82.9805933791714</v>
+        <v>81.9284793457735</v>
       </c>
       <c r="O83" s="15" t="n">
-        <v>-0.00607392183425228</v>
+        <v>-0.0123443865961455</v>
       </c>
       <c r="P83" s="16" t="n">
-        <v>-0.0661757883321553</v>
+        <v>-0.0725320979474119</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>-0.00605551286143968</v>
+        <v>-0.0122685072050317</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>1.01045342175611</v>
+        <v>1.01468647338811</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>0.963583199349017</v>
+        <v>0.990364966557821</v>
       </c>
     </row>
     <row r="84">
@@ -6304,46 +6362,46 @@
         <v>95.838</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>8.70759276517848</v>
+        <v>1.08938693789785</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>86.0508258181926</v>
+        <v>86.5567396236961</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>86.8051759675143</v>
+        <v>82.7540104013269</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>86.4622769929491</v>
+        <v>83.6458240883258</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>87.1304072348215</v>
+        <v>87.9742510819297</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>87.1304072348215</v>
+        <v>87.9742510819297</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>85.773419357371</v>
+        <v>86.1622300190654</v>
       </c>
       <c r="N84" s="14" t="n">
-        <v>85.773419357371</v>
+        <v>86.1622300190654</v>
       </c>
       <c r="O84" s="15" t="n">
-        <v>0.0331023950481587</v>
+        <v>0.0503852512408347</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>-0.0496225317015826</v>
+        <v>-0.0460107066103592</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>0.0336563751169878</v>
+        <v>0.0516761778944252</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>0.996776248709017</v>
+        <v>0.995442185018222</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>0.988114111875894</v>
+        <v>1.04118494803104</v>
       </c>
     </row>
     <row r="85">
@@ -6363,46 +6421,46 @@
         <v>89.752</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>2.16732825575618</v>
+        <v>1.00080602198701</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>87.5605457916726</v>
+        <v>89.2503992405649</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>87.4825289751142</v>
+        <v>82.7177301598905</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>86.5602610180994</v>
+        <v>82.5871824857932</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>87.5846717442438</v>
+        <v>89.6797161769725</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>87.5846717442438</v>
+        <v>89.6797161769725</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>86.9779257949022</v>
+        <v>88.1034093831974</v>
       </c>
       <c r="N85" s="14" t="n">
-        <v>86.9779257949022</v>
+        <v>88.1034093831974</v>
       </c>
       <c r="O85" s="15" t="n">
-        <v>0.0139451991681359</v>
+        <v>0.02227931639375</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>-0.00602414778075344</v>
+        <v>0.00151048292994949</v>
       </c>
       <c r="Q85" s="17" t="n">
-        <v>0.0140428870220579</v>
+        <v>0.0225293537980906</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>0.993346089936938</v>
+        <v>0.987148630514516</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>0.99423195481288</v>
+        <v>1.06510912730435</v>
       </c>
     </row>
     <row r="86">
@@ -6422,46 +6480,46 @@
         <v>77.378</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>-8.23395245629965</v>
+        <v>0.909473927452505</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>86.1039820804247</v>
+        <v>85.9360866743142</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>88.1529452402067</v>
+        <v>82.6268681080047</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>86.6316417907753</v>
+        <v>81.2981411852597</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>85.6119524562996</v>
+        <v>85.0799540969149</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>85.6119524562996</v>
+        <v>85.0799540969149</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>85.8375915592974</v>
+        <v>85.2010835223796</v>
       </c>
       <c r="N86" s="14" t="n">
-        <v>85.8375915592974</v>
+        <v>85.2010835223796</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>-0.0131973193604864</v>
+        <v>-0.0334970800548467</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>0.0281657125511749</v>
+        <v>0.0271860784835891</v>
       </c>
       <c r="Q86" s="17" t="n">
-        <v>-0.0131106165752188</v>
+        <v>-0.0329422650171735</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>0.996906176524119</v>
+        <v>0.991447095389389</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>0.973734811983874</v>
+        <v>1.03115470153135</v>
       </c>
     </row>
     <row r="87">
@@ -6481,113 +6539,165 @@
         <v>81.338</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>-3.20378958034653</v>
+        <v>1.00461053071864</v>
       </c>
       <c r="G87" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>83.7007608451273</v>
+        <v>79.995729620018</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>88.8206871942906</v>
+        <v>82.4959416028759</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>86.6922701605502</v>
+        <v>79.8264914118847</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>84.5417895803465</v>
+        <v>80.9647097187161</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>84.5417895803465</v>
+        <v>80.9647097187161</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>84.8985105389976</v>
+        <v>79.8683477784664</v>
       </c>
       <c r="N87" s="14" t="n">
-        <v>84.8985105389976</v>
+        <v>79.8683477784664</v>
       </c>
       <c r="O87" s="15" t="n">
-        <v>-0.0110004911515744</v>
+        <v>-0.06463452482244</v>
       </c>
       <c r="P87" s="16" t="n">
-        <v>0.0231128397824589</v>
+        <v>-0.025145487671173</v>
       </c>
       <c r="Q87" s="17" t="n">
-        <v>-0.0109402070030251</v>
+        <v>-0.0625899991343711</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>1.01430990210575</v>
+        <v>0.998407641980932</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>0.955841631277706</v>
+        <v>0.968148811040203</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
         <v>138</v>
       </c>
-      <c r="B88" s="2"/>
+      <c r="B88" s="2" t="n">
+        <v>78.735</v>
+      </c>
       <c r="C88" s="3" t="n">
-        <v>90.2048488769677</v>
+        <v>78.735</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>101.252076618742</v>
+        <v>78.735</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>79.1576211351935</v>
+        <v>78.735</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>9.20210043216632</v>
-      </c>
-      <c r="G88" s="7"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="9"/>
-      <c r="J88" s="10"/>
-      <c r="K88" s="11"/>
-      <c r="L88" s="12"/>
-      <c r="M88" s="13"/>
+        <v>1.08653925948282</v>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>72.6357453294825</v>
+      </c>
+      <c r="I88" s="9" t="n">
+        <v>82.3410011804539</v>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>78.2389334553856</v>
+      </c>
+      <c r="K88" s="11" t="n">
+        <v>72.4640175795184</v>
+      </c>
+      <c r="L88" s="12" t="n">
+        <v>72.4640175795184</v>
+      </c>
+      <c r="M88" s="13" t="n">
+        <v>73.449310800074</v>
+      </c>
       <c r="N88" s="14" t="n">
-        <v>81.0027484448014</v>
-      </c>
-      <c r="O88" s="15"/>
-      <c r="P88" s="16"/>
-      <c r="Q88" s="17"/>
-      <c r="R88" s="18"/>
-      <c r="S88" s="19"/>
+        <v>73.449310800074</v>
+      </c>
+      <c r="O88" s="15" t="n">
+        <v>-0.0837841070078302</v>
+      </c>
+      <c r="P88" s="16" t="n">
+        <v>-0.147546311373074</v>
+      </c>
+      <c r="Q88" s="17" t="n">
+        <v>-0.0803702237111142</v>
+      </c>
+      <c r="R88" s="18" t="n">
+        <v>1.0112006212217</v>
+      </c>
+      <c r="S88" s="19" t="n">
+        <v>0.892013817503951</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
         <v>139</v>
       </c>
-      <c r="B89" s="2"/>
+      <c r="B89" s="2" t="n">
+        <v>67.604</v>
+      </c>
       <c r="C89" s="3" t="n">
-        <v>85.533655568464</v>
+        <v>67.604</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>99.076448397322</v>
+        <v>67.604</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>71.990862739606</v>
+        <v>67.604</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>2.45625079644483</v>
-      </c>
-      <c r="G89" s="7"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="9"/>
-      <c r="J89" s="10"/>
-      <c r="K89" s="11"/>
-      <c r="L89" s="12"/>
-      <c r="M89" s="13"/>
+        <v>0.995574691957585</v>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>69.5610633792303</v>
+      </c>
+      <c r="I89" s="9" t="n">
+        <v>82.1771403567604</v>
+      </c>
+      <c r="J89" s="10" t="n">
+        <v>76.6078586970142</v>
+      </c>
+      <c r="K89" s="11" t="n">
+        <v>67.9044983225429</v>
+      </c>
+      <c r="L89" s="12" t="n">
+        <v>67.9044983225429</v>
+      </c>
+      <c r="M89" s="13" t="n">
+        <v>69.4243380748681</v>
+      </c>
       <c r="N89" s="14" t="n">
-        <v>83.0774047720192</v>
-      </c>
-      <c r="O89" s="15"/>
-      <c r="P89" s="16"/>
-      <c r="Q89" s="17"/>
-      <c r="R89" s="18"/>
-      <c r="S89" s="19"/>
+        <v>69.4243380748681</v>
+      </c>
+      <c r="O89" s="15" t="n">
+        <v>-0.0563580205670745</v>
+      </c>
+      <c r="P89" s="16" t="n">
+        <v>-0.212013036034581</v>
+      </c>
+      <c r="Q89" s="17" t="n">
+        <v>-0.0547993259754564</v>
+      </c>
+      <c r="R89" s="18" t="n">
+        <v>0.998034456379472</v>
+      </c>
+      <c r="S89" s="19" t="n">
+        <v>0.84481326283042</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
@@ -6595,16 +6705,16 @@
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="3" t="n">
-        <v>77.0846885072426</v>
+        <v>66.8246651811335</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>91.0513998588504</v>
+        <v>78.6149812648757</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>63.1179771556349</v>
+        <v>56.8026068914901</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>-8.2805208578632</v>
+        <v>0.911983259585936</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="8"/>
@@ -6614,7 +6724,7 @@
       <c r="L90" s="12"/>
       <c r="M90" s="13"/>
       <c r="N90" s="14" t="n">
-        <v>85.3652093651058</v>
+        <v>73.2740041867365</v>
       </c>
       <c r="O90" s="15"/>
       <c r="P90" s="16"/>
@@ -6628,16 +6738,16 @@
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3" t="n">
-        <v>79.2145364409065</v>
+        <v>72.7828104533536</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>93.4792039361543</v>
+        <v>89.0149265895745</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>64.9498689456587</v>
+        <v>59.5106652383537</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>-3.6633900831503</v>
+        <v>1.01087869915918</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="8"/>
@@ -6647,7 +6757,7 @@
       <c r="L91" s="12"/>
       <c r="M91" s="13"/>
       <c r="N91" s="14" t="n">
-        <v>82.8779265240568</v>
+        <v>71.9995490199687</v>
       </c>
       <c r="O91" s="15"/>
       <c r="P91" s="16"/>
@@ -6660,10 +6770,18 @@
         <v>142</v>
       </c>
       <c r="B92" s="2"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="6"/>
+      <c r="C92" s="3" t="n">
+        <v>71.8463563171369</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>88.3915045537389</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>58.3981338716862</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>1.08083521492496</v>
+      </c>
       <c r="G92" s="7"/>
       <c r="H92" s="8"/>
       <c r="I92" s="9"/>
@@ -6671,7 +6789,9 @@
       <c r="K92" s="11"/>
       <c r="L92" s="12"/>
       <c r="M92" s="13"/>
-      <c r="N92" s="14"/>
+      <c r="N92" s="14" t="n">
+        <v>66.4729972941574</v>
+      </c>
       <c r="O92" s="15"/>
       <c r="P92" s="16"/>
       <c r="Q92" s="17"/>
@@ -6683,10 +6803,18 @@
         <v>143</v>
       </c>
       <c r="B93" s="2"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="6"/>
+      <c r="C93" s="3" t="n">
+        <v>65.932906002413</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>81.437894807991</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>53.3799173489499</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>0.994546580300595</v>
+      </c>
       <c r="G93" s="7"/>
       <c r="H93" s="8"/>
       <c r="I93" s="9"/>
@@ -6694,7 +6822,9 @@
       <c r="K93" s="11"/>
       <c r="L93" s="12"/>
       <c r="M93" s="13"/>
-      <c r="N93" s="14"/>
+      <c r="N93" s="14" t="n">
+        <v>66.2944373932544</v>
+      </c>
       <c r="O93" s="15"/>
       <c r="P93" s="16"/>
       <c r="Q93" s="17"/>
@@ -7082,150 +7212,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B2" s="1"/>
+        <v>161</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3"/>
-      <c r="B3" s="1"/>
+      <c r="A3" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B4" s="1"/>
+        <v>163</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>0.0542005358875953</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>-0.0757078569600253</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>-0.110872699451926</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>165</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>-0.0163871180172237</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>166</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>0.0668383393898453</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>167</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>-0.0309046032288025</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>-0.240858450743497</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>169</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>-0.3395248383724</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>170</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>-0.181261752041887</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="1"/>
+      <c r="A14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="1"/>
+      <c r="A15" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="1"/>
+      <c r="A16" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="1"/>
+      <c r="A17" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="1"/>
+      <c r="A18" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="1"/>
+      <c r="A19" t="s">
+        <v>178</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7233,235 +7311,160 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
-    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6351555-507E-47C4-98ED-9D49028E9D04}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBB933BF-636B-4780-B093-4E0BAD8E8158}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4213C29E-54BE-4CBD-B322-A713586DE01B}"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0.0304441876656398</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>-0.0828607349041343</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>-0.119793533713121</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>-0.0184660334789974</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.0927967411659249</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>-0.00580498269678418</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>-0.25241421477093</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>-0.386959165100972</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>189</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>-0.227764759085469</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="1"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="1"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="1"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/indicadores/GR-EPUB_out.xlsx
+++ b/indicadores/GR-EPUB_out.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -23,7 +23,7 @@
     <t xml:space="preserve">Título</t>
   </si>
   <si>
-    <t xml:space="preserve">Ocupados en el sector público del Gran Rosario</t>
+    <t xml:space="preserve">Ocupados en el sector público</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
@@ -74,6 +74,12 @@
     <t xml:space="preserve">const</t>
   </si>
   <si>
+    <t xml:space="preserve">Alcance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aglomerado Gran Rosario</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resumen del correlograma</t>
   </si>
   <si>
@@ -107,13 +113,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">07/05/2026</t>
+    <t xml:space="preserve">17/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">vcorvalan</t>
+    <t xml:space="preserve">focampo</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1086,9 +1092,13 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7">
-      <c r="A7"/>
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
       <c r="B7"/>
-      <c r="C7"/>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
@@ -1099,7 +1109,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8"/>
       <c r="C8"/>
@@ -1113,12 +1123,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>-0.386959165100972</v>
+        <v>-0.393353214444826</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1129,7 +1139,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
@@ -1157,7 +1167,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
@@ -1171,12 +1181,12 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.00861123517101566</v>
+        <v>0.00864271842586174</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1199,7 +1209,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -1213,7 +1223,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -1227,7 +1237,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1241,12 +1251,12 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.624680655539973</v>
+        <v>0.687000047926634</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1257,7 +1267,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1271,12 +1281,12 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.145530738030723</v>
+        <v>0.118263621881725</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1419,10 +1429,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C32"/>
       <c r="D32"/>
@@ -1435,10 +1445,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33"/>
       <c r="D33"/>
@@ -1462,66 +1472,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>61.655</v>
@@ -1574,7 +1584,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>68.596</v>
@@ -1631,7 +1641,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>67.922</v>
@@ -1688,7 +1698,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>69.42</v>
@@ -1745,7 +1755,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>63.243</v>
@@ -1804,7 +1814,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>63.349</v>
@@ -1863,7 +1873,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>73.472</v>
@@ -1922,7 +1932,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>67.4</v>
@@ -1981,7 +1991,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>54.461</v>
@@ -2040,7 +2050,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>64.203</v>
@@ -2099,7 +2109,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>64.839</v>
@@ -2158,7 +2168,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>57.621</v>
@@ -2217,7 +2227,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>57.247</v>
@@ -2276,7 +2286,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>72.403</v>
@@ -2335,7 +2345,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>57.665</v>
@@ -2394,7 +2404,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>48.993</v>
@@ -2453,7 +2463,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>61.35</v>
@@ -2512,7 +2522,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>50.972</v>
@@ -2571,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>50.491</v>
@@ -2630,7 +2640,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>53.162</v>
@@ -2689,7 +2699,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>47.773</v>
@@ -2748,7 +2758,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>56.927</v>
@@ -2807,7 +2817,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>57.208</v>
@@ -2866,7 +2876,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>57.825</v>
@@ -2925,7 +2935,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>50.34</v>
@@ -2984,7 +2994,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>53.219</v>
@@ -3043,7 +3053,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>61.631</v>
@@ -3102,7 +3112,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>66.129</v>
@@ -3161,7 +3171,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>57.183</v>
@@ -3220,7 +3230,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>54.274</v>
@@ -3279,7 +3289,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>58.253</v>
@@ -3338,7 +3348,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>61.528</v>
@@ -3397,7 +3407,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>58.355</v>
@@ -3456,7 +3466,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>54.485</v>
@@ -3515,7 +3525,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>53.389</v>
@@ -3574,7 +3584,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>62.628</v>
@@ -3633,7 +3643,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>65.51</v>
@@ -3692,7 +3702,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>54.322</v>
@@ -3751,7 +3761,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>64.351</v>
@@ -3810,7 +3820,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>77.575</v>
@@ -3869,7 +3879,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>77.807</v>
@@ -3928,7 +3938,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>69.646</v>
@@ -3987,7 +3997,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>68.831</v>
@@ -4046,7 +4056,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>79.746</v>
@@ -4105,7 +4115,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>76.223</v>
@@ -4164,7 +4174,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>67.81</v>
@@ -4223,7 +4233,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>60.425</v>
@@ -4282,7 +4292,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>74.973</v>
@@ -4341,7 +4351,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>71.772</v>
@@ -4400,7 +4410,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>57.755</v>
@@ -4459,7 +4469,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>52.019</v>
@@ -4518,7 +4528,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>70.2</v>
@@ -4577,7 +4587,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>67.321</v>
@@ -4636,7 +4646,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>64.595</v>
@@ -4695,7 +4705,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>61.524</v>
@@ -4754,7 +4764,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>67.722</v>
@@ -4813,7 +4823,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>59.717</v>
@@ -4872,7 +4882,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>60.997</v>
@@ -4931,7 +4941,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>62.056</v>
@@ -4990,7 +5000,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>68.644</v>
@@ -5049,7 +5059,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>67.255</v>
@@ -5108,7 +5118,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>68.767</v>
@@ -5167,7 +5177,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>77.802</v>
@@ -5226,7 +5236,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>65.9</v>
@@ -5285,7 +5295,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>67.304</v>
@@ -5344,7 +5354,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>70.755</v>
@@ -5403,7 +5413,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>72.93</v>
@@ -5462,7 +5472,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>66.714</v>
@@ -5521,7 +5531,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>75.119</v>
@@ -5580,7 +5590,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>70.535</v>
@@ -5639,7 +5649,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>73.632</v>
@@ -5698,7 +5708,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>71.538</v>
@@ -5757,7 +5767,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>79.132</v>
@@ -5816,7 +5826,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>86.477</v>
@@ -5875,7 +5885,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>91.623</v>
@@ -5934,7 +5944,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>83.511</v>
@@ -5993,7 +6003,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>70.96</v>
@@ -6052,7 +6062,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>88.168</v>
@@ -6111,7 +6121,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>99.067</v>
@@ -6170,7 +6180,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>89.526</v>
@@ -6229,7 +6239,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>69.779</v>
@@ -6288,7 +6298,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>78.684</v>
@@ -6347,7 +6357,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>95.838</v>
@@ -6406,7 +6416,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>89.752</v>
@@ -6465,7 +6475,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>77.378</v>
@@ -6524,7 +6534,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>81.338</v>
@@ -6583,7 +6593,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>78.735</v>
@@ -6642,7 +6652,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>67.604</v>
@@ -6701,7 +6711,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="3" t="n">
@@ -6734,7 +6744,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3" t="n">
@@ -6767,7 +6777,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="3" t="n">
@@ -6800,7 +6810,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="3" t="n">
@@ -6833,7 +6843,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="3"/>
@@ -6856,7 +6866,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="3"/>
@@ -6879,7 +6889,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -6902,7 +6912,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="3"/>
@@ -6925,7 +6935,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" s="3"/>
@@ -6948,7 +6958,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" s="3"/>
@@ -6971,7 +6981,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" s="3"/>
@@ -6994,7 +7004,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" s="3"/>
@@ -7017,7 +7027,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" s="3"/>
@@ -7040,7 +7050,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B103" s="2"/>
       <c r="C103" s="3"/>
@@ -7063,7 +7073,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B104" s="2"/>
       <c r="C104" s="3"/>
@@ -7086,7 +7096,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" s="3"/>
@@ -7109,7 +7119,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B106" s="2"/>
       <c r="C106" s="3"/>
@@ -7132,7 +7142,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B107" s="2"/>
       <c r="C107" s="3"/>
@@ -7155,7 +7165,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B108" s="2"/>
       <c r="C108" s="3"/>
@@ -7178,7 +7188,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" s="3"/>
@@ -7212,97 +7222,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -7326,7 +7336,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -7336,80 +7346,80 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.0304441876656398</v>
+        <v>0.0242900109349527</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>-0.0828607349041343</v>
+        <v>-0.0849296970804645</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>-0.119793533713121</v>
+        <v>-0.114400378270245</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>-0.0184660334789974</v>
+        <v>-0.0130936923381602</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.0927967411659249</v>
+        <v>0.0929662219618596</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>-0.00580498269678418</v>
+        <v>-0.0083870450536254</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>-0.25241421477093</v>
+        <v>-0.257445905891771</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.386959165100972</v>
+        <v>-0.393353214444826</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.227764759085469</v>
+        <v>-0.229744332195104</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/GR-EPUB_out.xlsx
+++ b/indicadores/GR-EPUB_out.xlsx
@@ -56,10 +56,10 @@
     <t xml:space="preserve">Modelo</t>
   </si>
   <si>
-    <t xml:space="preserve">log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1 0 2)(1 0 0)</t>
+    <t xml:space="preserve">niv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1 0 2)(0 0 1)</t>
   </si>
   <si>
     <t xml:space="preserve">Código</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">17/06/2026</t>
+    <t xml:space="preserve">04/08/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">focampo</t>
+    <t xml:space="preserve">fleiva</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1108,9 +1108,7 @@
       <c r="J7" s="1"/>
     </row>
     <row r="8">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
+      <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
@@ -1122,14 +1120,10 @@
       <c r="J8" s="1"/>
     </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
+      <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
-      <c r="D9" t="n">
-        <v>-0.393353214444826</v>
-      </c>
+      <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9"/>
@@ -1139,13 +1133,11 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
+      <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
@@ -1154,10 +1146,14 @@
       <c r="J10" s="1"/>
     </row>
     <row r="11">
-      <c r="A11"/>
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
       <c r="B11"/>
       <c r="C11"/>
-      <c r="D11"/>
+      <c r="D11" t="n">
+        <v>-0.405851428014495</v>
+      </c>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
@@ -1167,11 +1163,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
-      <c r="D12"/>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12"/>
@@ -1180,14 +1178,10 @@
       <c r="J12" s="1"/>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
+      <c r="A13"/>
       <c r="B13"/>
       <c r="C13"/>
-      <c r="D13" t="n">
-        <v>0.00864271842586174</v>
-      </c>
+      <c r="D13"/>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
@@ -1196,7 +1190,9 @@
       <c r="J13" s="1"/>
     </row>
     <row r="14">
-      <c r="A14"/>
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -1209,11 +1205,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
-      <c r="D15"/>
+      <c r="D15" t="n">
+        <v>0.0139646458417521</v>
+      </c>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
@@ -1222,9 +1220,7 @@
       <c r="J15" s="1"/>
     </row>
     <row r="16">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
+      <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1237,7 +1233,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1251,13 +1247,11 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
-      <c r="D18" t="n">
-        <v>0.687000047926634</v>
-      </c>
+      <c r="D18"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -1267,7 +1261,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1286,7 +1280,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.118263621881725</v>
+        <v>0.460324025335458</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1296,7 +1290,9 @@
       <c r="J20" s="1"/>
     </row>
     <row r="21">
-      <c r="A21"/>
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1308,10 +1304,14 @@
       <c r="J21" s="1"/>
     </row>
     <row r="22">
-      <c r="A22"/>
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
       <c r="B22"/>
       <c r="C22"/>
-      <c r="D22"/>
+      <c r="D22" t="n">
+        <v>0.0680424094368654</v>
+      </c>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
@@ -1546,40 +1546,40 @@
         <v>61.655</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.912068749050234</v>
+        <v>-5.7113095216019</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>68.5129890185091</v>
+        <v>68.4122052687079</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>68.2161255338701</v>
+        <v>68.1657653405661</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>68.7182643027017</v>
+        <v>68.7513269393358</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>67.5990708641243</v>
+        <v>67.3663095216019</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>67.5990708641243</v>
+        <v>67.3663095216019</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>67.7699855752383</v>
+        <v>67.7037518192408</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>67.7699855752383</v>
+        <v>67.7037518192408</v>
       </c>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="18" t="n">
-        <v>0.989155290786247</v>
+        <v>0.989644341288453</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>0.993459904749204</v>
+        <v>0.993222205912058</v>
       </c>
     </row>
     <row r="3">
@@ -1599,44 +1599,44 @@
         <v>68.596</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.00710867861254</v>
+        <v>0.217363585481328</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>66.6698231412458</v>
+        <v>66.7819526393778</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>67.4354151223726</v>
+        <v>67.3671131689333</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>68.0939583984989</v>
+        <v>68.105919038224</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>68.1118149974662</v>
+        <v>68.3786364145187</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>68.1118149974662</v>
+        <v>68.3786364145187</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>66.8671451229149</v>
+        <v>66.9542256554844</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>66.8671451229149</v>
+        <v>66.9542256554844</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>-0.0134116640875042</v>
+        <v>-0.0111324099553934</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17" t="n">
-        <v>-0.0133221284416694</v>
+        <v>-0.0110706739821096</v>
       </c>
       <c r="R3" s="18" t="n">
-        <v>1.00295968959226</v>
+        <v>1.00257963430684</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>0.991573122247019</v>
+        <v>0.993871081986049</v>
       </c>
     </row>
     <row r="4">
@@ -1656,44 +1656,44 @@
         <v>67.922</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1.06718613038395</v>
+        <v>4.22867972870179</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>65.6951861357774</v>
+        <v>65.7779138698309</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>66.6543190517066</v>
+        <v>66.5679613374137</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>67.4640565271032</v>
+        <v>67.4535860500235</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>63.6458796326028</v>
+        <v>63.6933202712982</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>63.6458796326028</v>
+        <v>63.6933202712982</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>65.9971382929823</v>
+        <v>66.0195119364391</v>
       </c>
       <c r="N4" s="14" t="n">
-        <v>65.9971382929823</v>
+        <v>66.0195119364391</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>-0.0130963603225658</v>
+        <v>-0.0140588529967007</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17" t="n">
-        <v>-0.0130109761428178</v>
+        <v>-0.0139604888249298</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>1.00459626001486</v>
+        <v>1.00367293598101</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.990140462492543</v>
+        <v>0.991761060576955</v>
       </c>
     </row>
     <row r="5">
@@ -1713,44 +1713,44 @@
         <v>69.42</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1.01217498501891</v>
+        <v>1.10722921135851</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>67.8648574570971</v>
+        <v>67.5145391834103</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>65.8728744126253</v>
+        <v>65.7684423881488</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>66.8230520043165</v>
+        <v>66.7887664745271</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>68.5849789092575</v>
+        <v>68.3127707886415</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>68.5849789092575</v>
+        <v>68.3127707886415</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>67.5547653913786</v>
+        <v>67.2920200067629</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>67.5547653913786</v>
+        <v>67.2920200067629</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>0.0233272261631944</v>
+        <v>0.0190913224340363</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17" t="n">
-        <v>0.0236014339209909</v>
+        <v>0.0192747270162932</v>
       </c>
       <c r="R5" s="18" t="n">
-        <v>0.995430741663099</v>
+        <v>0.996704129520267</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>1.02553237571232</v>
+        <v>1.02316578534158</v>
       </c>
     </row>
     <row r="6">
@@ -1770,46 +1770,46 @@
         <v>63.243</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.91124008728697</v>
+        <v>-5.60621817847055</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>67.5373102603733</v>
+        <v>67.2413508769607</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>65.0892380212452</v>
+        <v>64.966892212614</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>66.1463472614684</v>
+        <v>66.087097482634</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>69.4032241143967</v>
+        <v>68.8492181784706</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>69.4032241143967</v>
+        <v>68.8492181784706</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>67.443380505377</v>
+        <v>67.1993135102407</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>67.443380505377</v>
+        <v>67.1993135102407</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>-0.00165016949732773</v>
+        <v>-0.00137862431401493</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>-0.00481931738791253</v>
+        <v>-0.00745066994731547</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>-0.00164880871625217</v>
+        <v>-0.00137767444806824</v>
       </c>
       <c r="R6" s="18" t="n">
-        <v>0.998609216822017</v>
+        <v>0.999374828640833</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>1.03616792200522</v>
+        <v>1.03436244557183</v>
       </c>
     </row>
     <row r="7">
@@ -1829,46 +1829,46 @@
         <v>63.349</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1.01549972180879</v>
+        <v>0.562953104619737</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>65.6626104075613</v>
+        <v>65.8490216345812</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>64.3032617589931</v>
+        <v>64.163236907535</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>65.4181543644129</v>
+        <v>65.331836266814</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>62.3820948834569</v>
+        <v>62.7860468953803</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>62.3820948834569</v>
+        <v>62.7860468953803</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>65.8456135910425</v>
+        <v>65.9813936768923</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>65.8456135910425</v>
+        <v>65.9813936768923</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>-0.0239756247174051</v>
+        <v>-0.0182902435607782</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>-0.0152770322404909</v>
+        <v>-0.014529807029623</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>-0.0236904927119874</v>
+        <v>-0.0181239921917175</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>1.00278702266549</v>
+        <v>1.00201023552097</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>1.02398559248565</v>
+        <v>1.02833642529565</v>
       </c>
     </row>
     <row r="8">
@@ -1888,46 +1888,46 @@
         <v>73.472</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1.06150338838846</v>
+        <v>3.9677372616617</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>67.2205199801498</v>
+        <v>67.4580560661646</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>63.5174937486039</v>
+        <v>63.3598290233659</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>64.6389697632689</v>
+        <v>64.520050623016</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>69.2150404828597</v>
+        <v>69.5042627383383</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>69.2150404828597</v>
+        <v>69.5042627383383</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>66.9325472226003</v>
+        <v>67.116161262313</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>66.9325472226003</v>
+        <v>67.116161262313</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>0.0163725405606158</v>
+        <v>0.0170520800700624</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>0.0141734771205591</v>
+        <v>0.0166109880807608</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>0.0165073050774271</v>
+        <v>0.0171982967043338</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>0.995715999256855</v>
+        <v>0.994931742422043</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>1.05376555768263</v>
+        <v>1.05928570668273</v>
       </c>
     </row>
     <row r="9">
@@ -1947,46 +1947,46 @@
         <v>67.4</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1.00720264898598</v>
+        <v>0.729927322804908</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>66.1322427663901</v>
+        <v>66.0508911894222</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>62.7332813835154</v>
+        <v>62.5581603668036</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>63.7941096107503</v>
+        <v>63.6360794003317</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>66.9180130412248</v>
+        <v>66.6700726771951</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>66.9180130412248</v>
+        <v>66.6700726771951</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>65.6803752390136</v>
+        <v>65.665369470319</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>65.6803752390136</v>
+        <v>65.665369470319</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>-0.0188851761307047</v>
+        <v>-0.0218531827491317</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>-0.027746231394718</v>
+        <v>-0.0241730079774763</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>-0.0187079684779111</v>
+        <v>-0.0216161318631416</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>0.993167213019332</v>
+        <v>0.994163262415375</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1.04697815562175</v>
+        <v>1.04966912526354</v>
       </c>
     </row>
     <row r="10">
@@ -2006,46 +2006,46 @@
         <v>54.461</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.912696556612417</v>
+        <v>-5.35606978854731</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>61.7172368289237</v>
+        <v>61.8855790968262</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>61.9555330238745</v>
+        <v>61.7635630156165</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>62.8917704131692</v>
+        <v>62.6891825084296</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>59.6704343907449</v>
+        <v>59.8170697885473</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>59.6704343907449</v>
+        <v>59.8170697885473</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>62.1530127442331</v>
+        <v>62.3039303925232</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>62.1530127442331</v>
+        <v>62.3039303925232</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>-0.0552008861158951</v>
+        <v>-0.0525471736497349</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>-0.0784416160859859</v>
+        <v>-0.0728487072560871</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>-0.053704968675106</v>
+        <v>-0.0511904388098382</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>1.00706084617037</v>
+        <v>1.00676007725552</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>1.0031874428436</v>
+        <v>1.00874896703692</v>
       </c>
     </row>
     <row r="11">
@@ -2065,46 +2065,46 @@
         <v>64.203</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1.02966699000025</v>
+        <v>1.29149068419706</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>61.4892203372124</v>
+        <v>61.8096764571996</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>61.1917724871139</v>
+        <v>60.9839389927671</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>61.9557681939899</v>
+        <v>61.7037898233623</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>62.3531691542179</v>
+        <v>62.9115093158029</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>62.3531691542179</v>
+        <v>62.9115093158029</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>61.5870886953201</v>
+        <v>61.8471520381575</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>61.5870886953201</v>
+        <v>61.8471520381575</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>-0.00914704268306189</v>
+        <v>-0.00735846045828472</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>-0.0646743900386667</v>
+        <v>-0.06265768890818</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>-0.00910533575004402</v>
+        <v>-0.00733145327249729</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>1.00159163439658</v>
+        <v>1.0006063060528</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>1.0064602836646</v>
+        <v>1.01415476041147</v>
       </c>
     </row>
     <row r="12">
@@ -2124,46 +2124,46 @@
         <v>64.839</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>1.04626988405914</v>
+        <v>3.09048026752337</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>60.8638436174968</v>
+        <v>60.8662952700228</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>60.4480954040206</v>
+        <v>60.2259737629511</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>60.9938122965646</v>
+        <v>60.6899706575831</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>61.9715820820998</v>
+        <v>61.7485197324766</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>61.9715820820998</v>
+        <v>61.7485197324766</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>60.8983828306202</v>
+        <v>60.8844231155974</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>60.8983828306202</v>
+        <v>60.8844231155974</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>-0.0112456296107084</v>
+        <v>-0.015688687577585</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>-0.0901529172632867</v>
+        <v>-0.0928500383441152</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>-0.0111826338813821</v>
+        <v>-0.0155662611912362</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>1.00056748327201</v>
+        <v>1.0002978306055</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.00744915821731</v>
+        <v>1.0109329797678</v>
       </c>
     </row>
     <row r="13">
@@ -2183,46 +2183,46 @@
         <v>57.621</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1.0056512710432</v>
+        <v>0.491856318366586</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>59.1985446966811</v>
+        <v>59.0618454858936</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>59.7313232782986</v>
+        <v>59.497557522316</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>60.0155990690466</v>
+        <v>59.6638329210075</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>57.2971980040631</v>
+        <v>57.1291436816334</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>57.2971980040631</v>
+        <v>57.1291436816334</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>59.6884656847209</v>
+        <v>59.4690719667325</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>59.6884656847209</v>
+        <v>59.4690719667325</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>-0.0200678227367567</v>
+        <v>-0.0235209853991864</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>-0.0912283087982954</v>
+        <v>-0.0943617245066634</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>-0.0198678041954651</v>
+        <v>-0.0232465231078517</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>1.00827589581045</v>
+        <v>1.00689491629475</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>0.999282493820236</v>
+        <v>0.999521231513194</v>
       </c>
     </row>
     <row r="14">
@@ -2242,46 +2242,46 @@
         <v>57.247</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.920549079992476</v>
+        <v>-4.62248077118634</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>61.9103005795985</v>
+        <v>61.1036602009658</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>59.0492297928258</v>
+        <v>58.8075320582403</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>59.0357137085171</v>
+        <v>58.6467772689255</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>62.1878846486576</v>
+        <v>61.8694807711863</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>62.1878846486576</v>
+        <v>61.8694807711863</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>61.5577372213206</v>
+        <v>60.5186481757805</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>61.5577372213206</v>
+        <v>60.5186481757805</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>0.0308367538855221</v>
+        <v>0.0174951733219142</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>-0.00957758114417007</v>
+        <v>-0.028654407603102</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>0.0313171316293053</v>
+        <v>0.0176491102742482</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>0.994305255264839</v>
+        <v>0.99042590864015</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.04248162824978</v>
+        <v>1.02909688704239</v>
       </c>
     </row>
     <row r="15">
@@ -2301,46 +2301,46 @@
         <v>72.403</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1.03743941231241</v>
+        <v>1.62773904998121</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.270480950306479</v>
+        <v>0</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>62.6180894370698</v>
+        <v>61.206487479116</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>58.4080673021836</v>
+        <v>58.163258899452</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>58.055149406732</v>
+        <v>57.64753091043</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>69.7900996826568</v>
+        <v>70.7752609500188</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>64.557981583904</v>
+        <v>61.206487479116</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>61.9005237257192</v>
+        <v>60.0299159308691</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>61.9005237257192</v>
+        <v>60.0299159308691</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>0.00555308948366181</v>
+        <v>-0.0081085150419673</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>0.00508929772520417</v>
+        <v>-0.0293826966546049</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>0.00556853646465472</v>
+        <v>-0.00807572970717907</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>0.988540600363226</v>
+        <v>0.980777012426201</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>1.05979407614134</v>
+        <v>1.03209340512787</v>
       </c>
     </row>
     <row r="16">
@@ -2360,46 +2360,46 @@
         <v>57.665</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1.02427700655566</v>
+        <v>1.82779200594211</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>58.3270618484548</v>
+        <v>57.4716508029022</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>57.8160498202384</v>
+        <v>57.5740132926249</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>57.0906602101483</v>
+        <v>56.6909345721256</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>56.298247086411</v>
+        <v>55.8372079940579</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>56.298247086411</v>
+        <v>55.8372079940579</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>58.2226068220825</v>
+        <v>57.1264247393107</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>58.2226068220825</v>
+        <v>57.1264247393107</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>-0.0612549278044888</v>
+        <v>-0.0495762471755454</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>-0.0439383754406074</v>
+        <v>-0.061723478419951</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>-0.0594165716583185</v>
+        <v>-0.0483674039274363</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>0.998209149868655</v>
+        <v>0.993993106883679</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.00703190555405</v>
+        <v>0.992225858026619</v>
       </c>
     </row>
     <row r="17">
@@ -2419,46 +2419,46 @@
         <v>48.993</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1.01912967508285</v>
+        <v>1.13328744058451</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>55.735951531604</v>
+        <v>55.6247954900109</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>57.2852350572825</v>
+        <v>57.0509725022947</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>56.1915143261086</v>
+        <v>55.81962376346</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>48.0733720132496</v>
+        <v>47.8597125594155</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>55.735951531604</v>
+        <v>55.6247954900109</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>55.4763383592418</v>
+        <v>55.2796951757922</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>55.4763383592418</v>
+        <v>55.2796951757922</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.0483171187099006</v>
+        <v>-0.0328611243771615</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>-0.070568530739723</v>
+        <v>-0.0704463118792881</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>-0.0471684215588769</v>
+        <v>-0.0323270635602664</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>0.995342087732816</v>
+        <v>0.993795926597507</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>0.968422985499983</v>
+        <v>0.968952723348734</v>
       </c>
     </row>
     <row r="18">
@@ -2478,46 +2478,46 @@
         <v>61.35</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.92792925813889</v>
+        <v>-4.09907356288004</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>54.1352032873481</v>
+        <v>54.0319817290891</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>56.8267320968997</v>
+        <v>56.604228289686</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>55.4030178963369</v>
+        <v>55.0719653609907</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>66.1149537660308</v>
+        <v>65.44907356288</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>54.1352032873481</v>
+        <v>54.0319817290891</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>53.4117535612821</v>
+        <v>53.3627615198093</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>53.4117535612821</v>
+        <v>53.3627615198093</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.0379257680852495</v>
+        <v>-0.0352925123697452</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>-0.132330784524306</v>
+        <v>-0.118242671832101</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>-0.0372155924313217</v>
+        <v>-0.0346769939647265</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>0.986636242553188</v>
+        <v>0.987614368604225</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>0.939905421100155</v>
+        <v>0.942734547085641</v>
       </c>
     </row>
     <row r="19">
@@ -2537,46 +2537,46 @@
         <v>50.972</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1.02681962658689</v>
+        <v>1.2097128689518</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>50.7443799709614</v>
+        <v>50.64285294568</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>56.4506817204701</v>
+        <v>56.2429810553901</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>54.7681992485847</v>
+        <v>54.4853520999079</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>49.6406561388284</v>
+        <v>49.7622871310482</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>49.6406561388284</v>
+        <v>49.7622871310482</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>50.8168008535157</v>
+        <v>50.7714469101994</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>50.8168008535157</v>
+        <v>50.7714469101994</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.0498038005209136</v>
+        <v>-0.0497790250206127</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>-0.179057012850414</v>
+        <v>-0.154230917653321</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>-0.0485839264720851</v>
+        <v>-0.048560354370865</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>1.00142717050826</v>
+        <v>1.00253923223199</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>0.900198178387783</v>
+        <v>0.902716142663168</v>
       </c>
     </row>
     <row r="20">
@@ -2596,46 +2596,46 @@
         <v>50.491</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1.01284460011627</v>
+        <v>0.961768350387827</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>49.7007713840009</v>
+        <v>49.4958454331148</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>56.165542503868</v>
+        <v>55.9748235458985</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>54.3237476375584</v>
+        <v>54.0919767972424</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>49.8506878490578</v>
+        <v>49.5292316496122</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>49.8506878490578</v>
+        <v>49.5292316496122</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>50.1331928669528</v>
+        <v>49.9479600549876</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>50.1331928669528</v>
+        <v>49.9479600549876</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>-0.0135437043820232</v>
+        <v>-0.0163524633471399</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>-0.138939398228071</v>
+        <v>-0.125659267442013</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>-0.0134524010776175</v>
+        <v>-0.016219487631864</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>1.00870049842106</v>
+        <v>1.00913439538039</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>0.892596966609914</v>
+        <v>0.892329030997856</v>
       </c>
     </row>
     <row r="21">
@@ -2655,46 +2655,46 @@
         <v>53.162</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1.0385081439211</v>
+        <v>2.19091021032212</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>50.4722507486255</v>
+        <v>50.3103915892284</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>55.9755167569791</v>
+        <v>55.8032980739996</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>54.080714602416</v>
+        <v>53.9004169451805</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>51.190739630867</v>
+        <v>50.9710897896779</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>51.190739630867</v>
+        <v>50.9710897896779</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>50.8265965160125</v>
+        <v>50.7047642496088</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>50.8265965160125</v>
+        <v>50.7047642496088</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>0.0137364500552421</v>
+        <v>0.0150382110819703</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>-0.0838148655940394</v>
+        <v>-0.0827596988665528</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>0.0138312285614823</v>
+        <v>0.0151518539253261</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>1.00702060562252</v>
+        <v>1.00783879130976</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>0.908014779688039</v>
+        <v>0.908633826308442</v>
       </c>
     </row>
     <row r="22">
@@ -2714,46 +2714,46 @@
         <v>47.773</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.935364279260359</v>
+        <v>-3.57464576946727</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>52.4421773290303</v>
+        <v>52.6234631583707</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>55.8808600055298</v>
+        <v>55.7279184575469</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>54.0277863833725</v>
+        <v>53.8964363101706</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>51.0742189532581</v>
+        <v>51.3476457694673</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>51.0742189532581</v>
+        <v>51.3476457694673</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>52.5097112809051</v>
+        <v>52.6457863473888</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>52.5097112809051</v>
+        <v>52.6457863473888</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>0.0325783582276755</v>
+        <v>0.0375663283860952</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>-0.0168884603150525</v>
+        <v>-0.0134358708582647</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>0.0331148430204711</v>
+        <v>0.03828086229185</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>1.00128777932791</v>
+        <v>1.00042420600391</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>0.939672569028265</v>
+        <v>0.944693213106353</v>
       </c>
     </row>
     <row r="23">
@@ -2773,46 +2773,46 @@
         <v>56.927</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.00400941351935</v>
+        <v>0.0102359390572445</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>55.5698661253937</v>
+        <v>55.7780175162899</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>55.8788372895429</v>
+        <v>55.7451783842161</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>54.1391993457855</v>
+        <v>54.0511520228834</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>56.6996675862371</v>
+        <v>56.9167640609428</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>56.6996675862371</v>
+        <v>56.9167640609428</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>55.2772227912564</v>
+        <v>55.4355163136838</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>55.2772227912564</v>
+        <v>55.4355163136838</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>0.0513628099842294</v>
+        <v>0.0516342730496454</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>0.08777455217219</v>
+        <v>0.0918640237244732</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>0.0527047558030989</v>
+        <v>0.0529905650546598</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>0.99473377651339</v>
+        <v>0.993859566584523</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>0.989233589540005</v>
+        <v>0.99444504297039</v>
       </c>
     </row>
     <row r="24">
@@ -2832,46 +2832,46 @@
         <v>57.208</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1.01011140730582</v>
+        <v>0.647108636617515</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>56.8012904151935</v>
+        <v>56.7459975964895</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>55.9637094983832</v>
+        <v>55.8488338712528</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>54.3744220178619</v>
+        <v>54.3229372612862</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>56.6353370392933</v>
+        <v>56.5608913633825</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>56.6353370392933</v>
+        <v>56.5608913633825</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>56.2016600955088</v>
+        <v>56.1774161453565</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>56.2016600955088</v>
+        <v>56.1774161453565</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>0.0165853562745113</v>
+        <v>0.0132943511514076</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>0.121046892917053</v>
+        <v>0.124718929131657</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>0.0167236568259466</v>
+        <v>0.0133831139494502</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>0.989443368006225</v>
+        <v>0.989980236929199</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>1.00425187320959</v>
+        <v>1.00588342229063</v>
       </c>
     </row>
     <row r="25">
@@ -2891,46 +2891,46 @@
         <v>57.825</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1.05450224308904</v>
+        <v>3.15388220628188</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>54.7112976856287</v>
+        <v>54.6048833894749</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>56.1302505403512</v>
+        <v>56.0333731769505</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>54.7057252690109</v>
+        <v>54.6844932635364</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>54.8362987172113</v>
+        <v>54.6711177937181</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>54.8362987172113</v>
+        <v>54.6711177937181</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>54.8263578923915</v>
+        <v>54.7551724541082</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>54.8263578923915</v>
+        <v>54.7551724541082</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>-0.0247752337730522</v>
+        <v>-0.0256429899078705</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.0786942595127134</v>
+        <v>0.079882201691347</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>-0.0244708466045315</v>
+        <v>-0.0253170008312277</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>1.00210304291125</v>
+        <v>1.00275230080726</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>0.976770232888551</v>
+        <v>0.977188581547539</v>
       </c>
     </row>
     <row r="26">
@@ -2950,46 +2950,46 @@
         <v>50.34</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.949856177339019</v>
+        <v>-2.77756286561426</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>53.1261017032144</v>
+        <v>53.2003981560019</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>56.3736540909603</v>
+        <v>56.2937295955356</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>55.1166845437488</v>
+        <v>55.1197110383021</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>52.9974970958502</v>
+        <v>53.1175628656143</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>52.9974970958502</v>
+        <v>53.1175628656143</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>53.8368911403838</v>
+        <v>53.8946597807724</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>53.8368911403838</v>
+        <v>53.8946597807724</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>-0.0182121206504598</v>
+        <v>-0.0158404416988176</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0.0252749410938273</v>
+        <v>0.0237221916516308</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>-0.0180472821840502</v>
+        <v>-0.0157156417333377</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>1.01337928841721</v>
+        <v>1.01304993287333</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>0.955000913254917</v>
+        <v>0.957383001055351</v>
       </c>
     </row>
     <row r="27">
@@ -3009,46 +3009,46 @@
         <v>53.219</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.976203955015673</v>
+        <v>-1.45339559814277</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>55.3987083573923</v>
+        <v>55.5022784014846</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>56.6883051058345</v>
+        <v>56.6239850116196</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>55.5915281538331</v>
+        <v>55.6124147169023</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>54.5162716526236</v>
+        <v>54.6723955981428</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>54.5162716526236</v>
+        <v>54.6723955981428</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>55.7808811331892</v>
+        <v>55.8904790413866</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>55.7808811331892</v>
+        <v>55.8904790413866</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.0354722375479484</v>
+        <v>0.0363626478084909</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.00911149866980132</v>
+        <v>0.00820706214998279</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.0361088828055895</v>
+        <v>0.0370318556371385</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>1.0068985863954</v>
+        <v>1.00699431899163</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>0.983992748222916</v>
+        <v>0.987046019984598</v>
       </c>
     </row>
     <row r="28">
@@ -3068,46 +3068,46 @@
         <v>61.631</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1.00771744972773</v>
+        <v>0.345445026008533</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>0.931043705967028</v>
+        <v>0.814528281312476</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>60.2087790632978</v>
+        <v>60.2827451027023</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>57.0664784424758</v>
+        <v>57.0162362056079</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>56.1038884737814</v>
+        <v>56.1364176897925</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>61.1590084270663</v>
+        <v>61.2855549739915</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>61.0934841316595</v>
+        <v>61.0995621036466</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>59.7238276340613</v>
+        <v>59.8131638631436</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>59.7238276340613</v>
+        <v>59.8131638631436</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>0.0682998849650126</v>
+        <v>0.0678317238303693</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>0.0626701690406828</v>
+        <v>0.0647190270976474</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>0.0706863430761768</v>
+        <v>0.0701852066584052</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>0.991945503018311</v>
+        <v>0.992210354077959</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>1.04656585203981</v>
+        <v>1.04905493318516</v>
       </c>
     </row>
     <row r="29">
@@ -3127,46 +3127,46 @@
         <v>66.129</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1.06330275452209</v>
+        <v>3.74786435286168</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>61.8646788542913</v>
+        <v>61.8702698538937</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>57.4990914374782</v>
+        <v>57.4613602145226</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>56.6220215956058</v>
+        <v>56.6608332518342</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>62.1920706203025</v>
+        <v>62.3811356471383</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>62.1920706203025</v>
+        <v>62.3811356471383</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>61.0956067564659</v>
+        <v>61.1429138782989</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>61.0956067564659</v>
+        <v>61.1429138782989</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>0.0227088974607901</v>
+        <v>0.0219882062202566</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>0.114347352351566</v>
+        <v>0.116660054893342</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>0.0229687074112155</v>
+        <v>0.0222317284234934</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>0.987568478297014</v>
+        <v>0.988243853189708</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>1.06254908084762</v>
+        <v>1.06407007509101</v>
       </c>
     </row>
     <row r="30">
@@ -3186,46 +3186,46 @@
         <v>57.183</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0.970769757213945</v>
+        <v>-1.52682211527237</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>59.0399085535178</v>
+        <v>59.0338746776783</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>57.979578305991</v>
+        <v>57.952786154072</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>57.1391315896073</v>
+        <v>57.1795904199585</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>58.9048016535991</v>
+        <v>58.7098221152724</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>58.9048016535991</v>
+        <v>58.7098221152724</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>59.1412268979363</v>
+        <v>59.1392383517845</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>59.1412268979363</v>
+        <v>59.1392383517845</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>-0.0325117012171616</v>
+        <v>-0.0333193388328414</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0.0985260412552615</v>
+        <v>0.0973116555952962</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>-0.0319888771433269</v>
+        <v>-0.032770363717087</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>1.0017160992776</v>
+        <v>1.001784800247</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>1.02003547845441</v>
+        <v>1.02047273783452</v>
       </c>
     </row>
     <row r="31">
@@ -3245,46 +3245,46 @@
         <v>54.274</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.959527885590254</v>
+        <v>-2.48217352945511</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>57.3889216956623</v>
+        <v>57.4958677091964</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>58.5043063751531</v>
+        <v>58.4870179996096</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>57.6762727712105</v>
+        <v>57.715219723073</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>56.5632336642445</v>
+        <v>56.7561735294551</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>56.5632336642445</v>
+        <v>56.7561735294551</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>57.6862898254512</v>
+        <v>57.779884666098</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>57.6862898254512</v>
+        <v>57.779884666098</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>-0.0249087259264401</v>
+        <v>-0.0232539366601336</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>0.0341588130835071</v>
+        <v>0.0338055006347742</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>-0.0246010634002574</v>
+        <v>-0.0229856474917804</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>1.00518162950274</v>
+        <v>1.00493978033931</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>0.986017840388424</v>
+        <v>0.987909567666516</v>
       </c>
     </row>
     <row r="32">
@@ -3304,46 +3304,46 @@
         <v>58.253</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.992150233663501</v>
+        <v>-0.644369490209566</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>57.7841191736944</v>
+        <v>57.9129829053621</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>59.0702212366956</v>
+        <v>59.061032873965</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>58.2633278061602</v>
+        <v>58.2979028485615</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>58.7138903197166</v>
+        <v>58.8973694902096</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>58.7138903197166</v>
+        <v>58.8973694902096</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>57.9123062432034</v>
+        <v>57.9968929626261</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>57.9123062432034</v>
+        <v>57.9968929626261</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>0.00391037111937579</v>
+        <v>0.00374874055244049</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>-0.0303316358415169</v>
+        <v>-0.0303657386302656</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>0.00391802659585361</v>
+        <v>0.00375577586875009</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>1.00221837887887</v>
+        <v>1.00144889890063</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>0.980397652670837</v>
+        <v>0.981982368753866</v>
       </c>
     </row>
     <row r="33">
@@ -3363,46 +3363,46 @@
         <v>61.528</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1.06711601497782</v>
+        <v>4.0913406593697</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>58.2709606648425</v>
+        <v>58.0835810609743</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>59.6730553119052</v>
+        <v>59.6707261221738</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>58.9246141646662</v>
+        <v>58.9530262528401</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>57.658210669136</v>
+        <v>57.4366593406303</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>57.658210669136</v>
+        <v>57.4366593406303</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>58.0976357330264</v>
+        <v>57.9635970924678</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>58.0976357330264</v>
+        <v>57.9635970924678</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>0.00319506491126918</v>
+        <v>-0.000574262338104104</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>-0.049070157129134</v>
+        <v>-0.0519981234809869</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>0.00320017457161237</v>
+        <v>-0.000574097481046199</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>0.997025535020556</v>
+        <v>0.997934287688279</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.97359914670626</v>
+        <v>0.971390845383535</v>
       </c>
     </row>
     <row r="34">
@@ -3422,46 +3422,46 @@
         <v>58.355</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.999910362347738</v>
+        <v>0.271299801599014</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>58.0916886747991</v>
+        <v>57.9130809476987</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>60.3083183152455</v>
+        <v>60.3118907996566</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>59.686702129506</v>
+        <v>59.7089737255331</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>58.3602312741169</v>
+        <v>58.083700198401</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>58.3602312741169</v>
+        <v>58.083700198401</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>57.9543976358865</v>
+        <v>57.8354378008692</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>57.9543976358865</v>
+        <v>57.8354378008692</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>-0.0024685163321614</v>
+        <v>-0.00221347861910784</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>-0.0200677145926991</v>
+        <v>-0.0220462858036798</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>-0.00246547205118797</v>
+        <v>-0.00221103068179462</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>0.997636649199833</v>
+        <v>0.998659315899638</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.960968557155673</v>
+        <v>0.958939224654493</v>
       </c>
     </row>
     <row r="35">
@@ -3481,46 +3481,46 @@
         <v>54.485</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.948572893367717</v>
+        <v>-3.25269146604436</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>56.9636065955074</v>
+        <v>57.2250175751796</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>60.9702606832784</v>
+        <v>60.9789236700958</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>60.5698299659796</v>
+        <v>60.5865472217035</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>57.4389173261761</v>
+        <v>57.7376914660444</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>57.4389173261761</v>
+        <v>57.7376914660444</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>57.102148597788</v>
+        <v>57.2951468441532</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>57.102148597788</v>
+        <v>57.2951468441532</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>-0.0148147089976633</v>
+        <v>-0.00938577572045307</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.0101261708705944</v>
+        <v>-0.00838938714997528</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>-0.0147055111063862</v>
+        <v>-0.00934186680796278</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>1.00243211430176</v>
+        <v>1.00122550017362</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.936557396308604</v>
+        <v>0.939589343264367</v>
       </c>
     </row>
     <row r="36">
@@ -3540,46 +3540,46 @@
         <v>53.389</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.967708693132723</v>
+        <v>-2.23250424612316</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>56.1617126904299</v>
+        <v>56.4280821964011</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>61.6519152981651</v>
+        <v>61.6648288780477</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>61.58760358511</v>
+        <v>61.5984223287788</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>55.1705284646829</v>
+        <v>55.6215042461232</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>55.1705284646829</v>
+        <v>55.6215042461232</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>56.5211445148424</v>
+        <v>56.7302099330552</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>56.5211445148424</v>
+        <v>56.7302099330552</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>-0.0102269372937026</v>
+        <v>-0.00990905092728083</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>-0.0240218671748068</v>
+        <v>-0.0218405325676195</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>-0.0101748199886139</v>
+        <v>-0.0098601180416682</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>1.00639994414689</v>
+        <v>1.00535420884237</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.916778404068894</v>
+        <v>0.919976767392778</v>
       </c>
     </row>
     <row r="37">
@@ -3599,46 +3599,46 @@
         <v>62.628</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1.07415188362687</v>
+        <v>4.68786022607007</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>57.6484337399347</v>
+        <v>57.5183436852083</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>62.3441079524687</v>
+        <v>62.3605847979415</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>62.7379743347211</v>
+        <v>62.7430303554083</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>58.3046038038278</v>
+        <v>57.9401397739299</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>58.3046038038278</v>
+        <v>57.9401397739299</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>57.9718352337997</v>
+        <v>57.8259855712447</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>57.9718352337997</v>
+        <v>57.8259855712447</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>0.0253424858444698</v>
+        <v>0.0191313801092093</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>-0.0021653290644168</v>
+        <v>-0.00237410250788195</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>0.0256663365791598</v>
+        <v>0.0193155576100039</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>1.00560989211474</v>
+        <v>1.00534858736058</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.929868709934828</v>
+        <v>0.927284209386592</v>
       </c>
     </row>
     <row r="38">
@@ -3658,46 +3658,46 @@
         <v>65.51</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.02315053800393</v>
+        <v>1.80440265636588</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>60.1076048628604</v>
+        <v>59.8021584909958</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>63.0336135719811</v>
+        <v>63.053392726311</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>63.9868081870347</v>
+        <v>63.9889180198278</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>64.0277237480653</v>
+        <v>63.7055973436341</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>60.1076048628604</v>
+        <v>59.8021584909958</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>60.4290330820978</v>
+        <v>60.1441706101468</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>60.4290330820978</v>
+        <v>60.1441706101468</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.0415123764306539</v>
+        <v>0.0393062715062933</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>0.0426997009227641</v>
+        <v>0.0399189994416012</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>0.0423860627904602</v>
+        <v>0.0400889844937615</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1.00534754662028</v>
+        <v>1.00571905977612</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>0.958679499043648</v>
+        <v>0.953860974162136</v>
       </c>
     </row>
     <row r="39">
@@ -3717,46 +3717,46 @@
         <v>54.322</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.944794708199529</v>
+        <v>-3.65308574228602</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>63.1963187988425</v>
+        <v>63.0322256846657</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>63.7046823924017</v>
+        <v>63.7276911815504</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>65.2778042616183</v>
+        <v>65.280617587366</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>57.4960883338562</v>
+        <v>57.975085742286</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>63.1963187988425</v>
+        <v>63.0322256846657</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>63.6640990744683</v>
+        <v>63.5178337631902</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>63.6640990744683</v>
+        <v>63.5178337631902</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>0.0521511402737783</v>
+        <v>0.0545761896208371</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.114915999446902</v>
+        <v>0.108607574319743</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>0.0535349620434182</v>
+        <v>0.0560929366689813</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>1.0074020177839</v>
+        <v>1.00770412393422</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.999362946075402</v>
+        <v>0.99670696655615</v>
       </c>
     </row>
     <row r="40">
@@ -3776,46 +3776,46 @@
         <v>64.351</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.94417006208405</v>
+        <v>-3.85372519243351</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>67.7638697558548</v>
+        <v>67.8747269244831</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>64.3397358939862</v>
+        <v>64.3658866606563</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>66.5352656614184</v>
+        <v>66.541727525707</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>68.156153837328</v>
+        <v>68.2047251924335</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>68.156153837328</v>
+        <v>68.2047251924335</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>67.8447698508065</v>
+        <v>67.9452137371071</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>67.8447698508065</v>
+        <v>67.9452137371071</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>0.0636014894207722</v>
+        <v>0.0673809869715937</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0.200343171270894</v>
+        <v>0.197690151636778</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>0.0656676343043507</v>
+        <v>0.069702943435118</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>1.00119385293731</v>
+        <v>1.00103848392204</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>1.05447697147212</v>
+        <v>1.05560906968192</v>
       </c>
     </row>
     <row r="41">
@@ -3835,46 +3835,46 @@
         <v>77.575</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1.0793726328099</v>
+        <v>5.2358211211045</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>72.1207493973095</v>
+        <v>72.4573537431372</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>64.9208778297449</v>
+        <v>64.9499509946904</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>67.6730880620675</v>
+        <v>67.684604343022</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>71.8704529297275</v>
+        <v>72.3391788788955</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>71.8704529297275</v>
+        <v>72.3391788788955</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>71.6419708807077</v>
+        <v>71.90503439478</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>71.6419708807077</v>
+        <v>71.90503439478</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.0544587883989465</v>
+        <v>0.0566445815700355</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.235806501411875</v>
+        <v>0.243472699763832</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0559689573455908</v>
+        <v>0.0582796114674728</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>0.993361431757119</v>
+        <v>0.9923773182455</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>1.10352745180971</v>
+        <v>1.10708373591626</v>
       </c>
     </row>
     <row r="42">
@@ -3894,46 +3894,46 @@
         <v>77.807</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.04200002106925</v>
+        <v>3.06994537110434</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>74.1453054360598</v>
+        <v>74.2414888623469</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>65.4325972139022</v>
+        <v>65.4642552887963</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>68.6132715800778</v>
+        <v>68.6299195358152</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>74.6708238260478</v>
+        <v>74.7370546288957</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>74.6708238260478</v>
+        <v>74.7370546288957</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>73.7924299844307</v>
+        <v>73.8572135166655</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>73.7924299844307</v>
+        <v>73.8572135166655</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>0.0295750638968236</v>
+        <v>0.0267874004833489</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.221141994514089</v>
+        <v>0.228002859918152</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>0.0300167496411257</v>
+        <v>0.0271494080813235</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>0.995240758001417</v>
+        <v>0.994823981151646</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>1.12776250869578</v>
+        <v>1.12820673191566</v>
       </c>
     </row>
     <row r="43">
@@ -3953,46 +3953,46 @@
         <v>69.646</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.941701485344581</v>
+        <v>-3.96956592997531</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>74.4646514136876</v>
+        <v>74.1187274342968</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>65.8637265451203</v>
+        <v>65.8977889155453</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>69.2988031562999</v>
+        <v>69.3216174732706</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>73.9576193558998</v>
+        <v>73.6155659299753</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>73.9576193558998</v>
+        <v>73.6155659299753</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>74.2185787161687</v>
+        <v>73.9773116328798</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>74.2185787161687</v>
+        <v>73.9773116328798</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>0.0057583542335307</v>
+        <v>0.00162476447924383</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.165783852989967</v>
+        <v>0.16466993992089</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>0.00577496542433775</v>
+        <v>0.00162608512419915</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>0.996695442832978</v>
+        <v>0.998092036839915</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.12685058391473</v>
+        <v>1.12260688636593</v>
       </c>
     </row>
     <row r="44">
@@ -4012,46 +4012,46 @@
         <v>68.831</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.926539497755063</v>
+        <v>-5.11006004267282</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>73.983270873572</v>
+        <v>73.8324832033331</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>66.2088722136939</v>
+        <v>66.2453367470966</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>69.702957492814</v>
+        <v>69.7341782000375</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>74.2882523268273</v>
+        <v>73.9410600426728</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>74.2882523268273</v>
+        <v>73.9410600426728</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>73.9622414541335</v>
+        <v>73.8312474388553</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>73.9622414541335</v>
+        <v>73.8312474388553</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>-0.00345979347989248</v>
+        <v>-0.00197639761171382</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.0901686543676046</v>
+        <v>0.0866291145175062</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>-0.0034538152908512</v>
+        <v>-0.00197444582400197</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>0.999715754397039</v>
+        <v>0.99998326259088</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>1.11710468674674</v>
+        <v>1.11451237270813</v>
       </c>
     </row>
     <row r="45">
@@ -4071,46 +4071,46 @@
         <v>79.746</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1.08771973088276</v>
+        <v>5.91869625989959</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>73.5168698229445</v>
+        <v>73.7484155891347</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>66.4676992929241</v>
+        <v>66.5065072662427</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>69.8223033726984</v>
+        <v>69.8635515030487</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>73.3148418069796</v>
+        <v>73.8273037401004</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>73.3148418069796</v>
+        <v>73.8273037401004</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>73.4402499350255</v>
+        <v>73.6156111158844</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>73.4402499350255</v>
+        <v>73.6156111158844</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>-0.00708256280105702</v>
+        <v>-0.00292493822954247</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.0251009154579538</v>
+        <v>0.0237893874260988</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>-0.00705754056185148</v>
+        <v>-0.00292066476527419</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>0.998957791754416</v>
+        <v>0.998199222692591</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>1.10490133878974</v>
+        <v>1.10689335738505</v>
       </c>
     </row>
     <row r="46">
@@ -4130,46 +4130,46 @@
         <v>76.223</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1.04640024766114</v>
+        <v>3.35622305933585</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>73.012278575068</v>
+        <v>73.1303829412917</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>66.6449224686833</v>
+        <v>66.6857187828366</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>69.6763360532014</v>
+        <v>69.72672157845</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>72.8430637993155</v>
+        <v>72.8667769406642</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>72.8430637993155</v>
+        <v>72.8667769406642</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>72.7320336356489</v>
+        <v>72.8217996671948</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>72.7320336356489</v>
+        <v>72.8217996671948</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>-0.00969023434399572</v>
+        <v>-0.010841754440389</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>-0.0143699882088935</v>
+        <v>-0.0140191296174078</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>-0.0096434353097008</v>
+        <v>-0.0107831944428201</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>0.996161673832286</v>
+        <v>0.99578036840933</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.0913364580749</v>
+        <v>1.09201491708203</v>
       </c>
     </row>
     <row r="47">
@@ -4189,46 +4189,46 @@
         <v>67.81</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.942759246396773</v>
+        <v>-3.91634104735057</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>70.9872570002078</v>
+        <v>70.882498072247</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>66.7495358909147</v>
+        <v>66.7919651045269</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>69.302013483743</v>
+        <v>69.3604913835728</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>71.9271651369848</v>
+        <v>71.7263410473506</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>71.9271651369848</v>
+        <v>71.7263410473506</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>70.9423177388861</v>
+        <v>70.8638865828901</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>70.9423177388861</v>
+        <v>70.8638865828901</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>-0.0249147945857377</v>
+        <v>-0.0272544096658414</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>-0.0441434076744024</v>
+        <v>-0.0420862151011975</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>-0.0246069827461215</v>
+        <v>-0.0268863594864817</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.999366939036374</v>
+        <v>0.999737431808089</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>1.06281364794541</v>
+        <v>1.06096424131242</v>
       </c>
     </row>
     <row r="48">
@@ -4248,46 +4248,46 @@
         <v>60.425</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.920429916259623</v>
+        <v>-5.52552018026204</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>0.512904979973657</v>
+        <v>0.552564962112028</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>68.5704957821978</v>
+        <v>68.6002168189724</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>66.7944075478935</v>
+        <v>66.8381032003112</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>68.7521272524735</v>
+        <v>68.8173641525593</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>65.648670183984</v>
+        <v>65.950520180262</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>67.0718768822594</v>
+        <v>67.136087296195</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>68.6583473498603</v>
+        <v>68.6759475477144</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>68.6583473498603</v>
+        <v>68.6759475477144</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>-0.0327244029489378</v>
+        <v>-0.0313619172395015</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>-0.071710835150424</v>
+        <v>-0.0698254474897013</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>-0.0321947528896971</v>
+        <v>-0.0308752333618679</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>1.00128118612328</v>
+        <v>1.00110394299397</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>1.02790562668933</v>
+        <v>1.02749695547007</v>
       </c>
     </row>
     <row r="49">
@@ -4307,46 +4307,46 @@
         <v>74.973</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.09349910316104</v>
+        <v>6.267725448883</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>68.3840454271175</v>
+        <v>68.6771546140446</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>66.7956414461735</v>
+        <v>66.8400740241512</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>68.0925947058094</v>
+        <v>68.1616723678708</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>68.5624704979376</v>
+        <v>68.705274551117</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>68.5624704979376</v>
+        <v>68.705274551117</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>68.1053972843686</v>
+        <v>68.3443462938477</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>68.1053972843686</v>
+        <v>68.3443462938477</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>-0.00808625239047259</v>
+        <v>-0.00484018668985849</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>-0.0726420819016385</v>
+        <v>-0.0716052579355588</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>-0.00805364659702701</v>
+        <v>-0.0048284918622532</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>0.995925246290878</v>
+        <v>0.995154017051708</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>1.01960840273164</v>
+        <v>1.02250554464008</v>
       </c>
     </row>
     <row r="50">
@@ -4366,46 +4366,46 @@
         <v>71.772</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1.03726712268429</v>
+        <v>2.74183332652854</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>0.599401568615847</v>
+        <v>0.887687684970335</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>66.7755017499598</v>
+        <v>67.2546009533908</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>66.7695150106425</v>
+        <v>66.8140047700686</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>67.3809319383163</v>
+        <v>67.4493421276866</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>69.193362471824</v>
+        <v>69.0301666734715</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>68.2247712593398</v>
+        <v>68.8307487769619</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>66.4927558679657</v>
+        <v>66.9254252904931</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>66.4927558679657</v>
+        <v>66.9254252904931</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>-0.023963457880275</v>
+        <v>-0.02097989864136</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>-0.0857844536416895</v>
+        <v>-0.0809699074130134</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>-0.0236786140409608</v>
+        <v>-0.0207613516011114</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>0.995765724336257</v>
+        <v>0.995105529462202</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.995855007444151</v>
+        <v>1.00166762224189</v>
       </c>
     </row>
     <row r="51">
@@ -4425,46 +4425,46 @@
         <v>57.755</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.947439920180495</v>
+        <v>-3.5799290569314</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>62.1480723790958</v>
+        <v>62.5243068802355</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>66.7334099343457</v>
+        <v>66.7771883824145</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>66.6770044235203</v>
+        <v>66.7390175411024</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>60.9590104552458</v>
+        <v>61.3349290569314</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>60.9590104552458</v>
+        <v>61.3349290569314</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>62.7160926316845</v>
+        <v>63.015263187659</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>62.7160926316845</v>
+        <v>63.015263187659</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>-0.0584749319121856</v>
+        <v>-0.0602019742508354</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>-0.115956531579353</v>
+        <v>-0.110756321360536</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>-0.056798115629025</v>
+        <v>-0.0584256593941966</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.00913978874717</v>
+        <v>1.0078522471007</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.93980050912109</v>
+        <v>0.943664516493086</v>
       </c>
     </row>
     <row r="52">
@@ -4484,46 +4484,46 @@
         <v>52.019</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.929475457093237</v>
+        <v>-4.84855990918533</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>0</v>
+        <v>0.0562300831461937</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>60.7215783569066</v>
+        <v>60.7804690671044</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>66.7056174454837</v>
+        <v>66.7481782705442</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>66.0448968315526</v>
+        <v>66.09624975046</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>55.9659747904262</v>
+        <v>56.8675599091853</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>60.7215783569066</v>
+        <v>60.5604458598111</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>61.6533305914038</v>
+        <v>61.6338827682326</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>61.6533305914038</v>
+        <v>61.6338827682326</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>-0.0170908231569803</v>
+        <v>-0.0221652056091492</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>-0.102027168273673</v>
+        <v>-0.102540482234907</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>-0.0169456035235166</v>
+        <v>-0.0219213623739478</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>1.01534466428097</v>
+        <v>1.01404091995713</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.924259949198297</v>
+        <v>0.923379249669073</v>
       </c>
     </row>
     <row r="53">
@@ -4543,46 +4543,46 @@
         <v>70.2</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.0927647133772</v>
+        <v>6.12028970362324</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>0.94479850650331</v>
+        <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>63.7050145797987</v>
+        <v>63.5797561002009</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>66.7008197725827</v>
+        <v>66.7421264317345</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>65.5201038627032</v>
+        <v>65.5595694556806</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>64.2407273410634</v>
+        <v>64.0797102963768</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>64.2111551965563</v>
+        <v>64.0797102963768</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>63.8715891714559</v>
+        <v>63.7101599262934</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>63.8715891714559</v>
+        <v>63.7101599262934</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>0.0353473962656272</v>
+        <v>0.0331322820889818</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>-0.062165529924666</v>
+        <v>-0.0678064334338574</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>0.0359795417177573</v>
+        <v>0.0336872685089218</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>1.00261477990007</v>
+        <v>1.00205102746678</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>0.957583270928707</v>
+        <v>0.954571922299446</v>
       </c>
     </row>
     <row r="54">
@@ -4602,46 +4602,46 @@
         <v>67.321</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1.01474970851465</v>
+        <v>1.20022674739081</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>66.6036868350842</v>
+        <v>66.4516334107839</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>66.7299591197385</v>
+        <v>66.7703175305057</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>65.1115036248887</v>
+        <v>65.1398283372321</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>66.3424679358044</v>
+        <v>66.1207732526092</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>66.3424679358044</v>
+        <v>66.1207732526092</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>66.09745009335</v>
+        <v>65.9535099715953</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>66.09745009335</v>
+        <v>65.9535099715953</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>0.0342555210053571</v>
+        <v>0.0346060531063525</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>-0.00594509536348109</v>
+        <v>-0.014522362983562</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>0.0348489986043565</v>
+        <v>0.0352118099828527</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>0.992399268482124</v>
+        <v>0.992503969976037</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.990521363496514</v>
+        <v>0.987766906177476</v>
       </c>
     </row>
     <row r="55">
@@ -4661,46 +4661,46 @@
         <v>64.595</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.957052155896103</v>
+        <v>-2.89778308478587</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>66.8193840645143</v>
+        <v>66.8298608909741</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>66.8024216506868</v>
+        <v>66.8423722212933</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>64.8214294826949</v>
+        <v>64.8404787797859</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>67.493709305235</v>
+        <v>67.4927830847859</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>67.493709305235</v>
+        <v>67.4927830847859</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>66.4230899029743</v>
+        <v>66.4155444889073</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>66.4230899029743</v>
+        <v>66.4155444889073</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>0.00491456592409731</v>
+        <v>0.00698103337860492</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>0.0591075928958154</v>
+        <v>0.0539596461118057</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>0.00492666221109017</v>
+        <v>0.00700545759446403</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>0.994069173682335</v>
+        <v>0.993800429979307</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>0.994321586877553</v>
+        <v>0.993614413758792</v>
       </c>
     </row>
     <row r="56">
@@ -4720,46 +4720,46 @@
         <v>61.524</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.955898632690373</v>
+        <v>-3.03183853344837</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>65.016766598837</v>
+        <v>65.084394161127</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>66.9273513471735</v>
+        <v>66.9675051933594</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>64.6583696222625</v>
+        <v>64.6698778925901</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>64.362473065623</v>
+        <v>64.5558385334484</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>64.362473065623</v>
+        <v>64.5558385334484</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>64.7825113977727</v>
+        <v>64.8257168540165</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>64.7825113977727</v>
+        <v>64.8257168540165</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>-0.0250090544419944</v>
+        <v>-0.0242287431737351</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>0.0507544487273031</v>
+        <v>0.0517870032265604</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>-0.0246989188187131</v>
+        <v>-0.0239375833944472</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>0.996397003214422</v>
+        <v>0.996025509487419</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>0.967952714305474</v>
+        <v>0.968017498439598</v>
       </c>
     </row>
     <row r="57">
@@ -4779,46 +4779,46 @@
         <v>67.722</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1.07646643689748</v>
+        <v>5.0235927356166</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>62.1982217405433</v>
+        <v>62.1026784879471</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>67.1143242457286</v>
+        <v>67.1553376427554</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>64.6441736288447</v>
+        <v>64.649644306418</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>62.9113901546098</v>
+        <v>62.6984072643834</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>62.9113901546098</v>
+        <v>62.6984072643834</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>62.5943725247505</v>
+        <v>62.5157964357306</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>62.5943725247505</v>
+        <v>62.5157964357306</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>-0.0343603028012247</v>
+        <v>-0.0362831218793297</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>-0.0199966317305321</v>
+        <v>-0.0187468292646672</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>-0.0337766910514903</v>
+        <v>-0.0356327786314758</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1.00636916575943</v>
+        <v>1.00665217600661</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>0.932652950442755</v>
+        <v>0.930913291930633</v>
       </c>
     </row>
     <row r="58">
@@ -4838,46 +4838,46 @@
         <v>59.717</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0.992104684091785</v>
+        <v>-0.393532680707186</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>61.3109186095921</v>
+        <v>61.2159127595121</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>67.3713133339558</v>
+        <v>67.4139834738704</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>64.7992116049114</v>
+        <v>64.8008264552473</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>60.1922367241593</v>
+        <v>60.1105326807072</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>60.1922367241593</v>
+        <v>60.1105326807072</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>61.5663317801837</v>
+        <v>61.5037473464141</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>61.5663317801837</v>
+        <v>61.5037473464141</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>-0.0165602191844207</v>
+        <v>-0.0163211623617376</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>-0.0685520894795036</v>
+        <v>-0.0674681700351892</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>-0.0164238525461745</v>
+        <v>-0.0161886938504719</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>1.00416586762006</v>
+        <v>1.00470195695738</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>0.913836004279786</v>
+        <v>0.912329225734789</v>
       </c>
     </row>
     <row r="59">
@@ -4897,46 +4897,46 @@
         <v>60.997</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.96867587227818</v>
+        <v>-2.0985167598587</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>61.911222451334</v>
+        <v>62.0191072291992</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>67.7036647656524</v>
+        <v>67.7487710096073</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>65.1351897355614</v>
+        <v>65.1347165878451</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>62.9694635178062</v>
+        <v>63.0955167598587</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>62.9694635178062</v>
+        <v>63.0955167598587</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>62.2258257926454</v>
+        <v>62.3010009373276</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>62.2258257926454</v>
+        <v>62.3010009373276</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.0106549601306464</v>
+        <v>0.0128793866559137</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>-0.0631898352886019</v>
+        <v>-0.0619515142613479</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.0107119263628763</v>
+        <v>0.0129626831747833</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>1.00508152365363</v>
+        <v>1.00454527194477</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>0.91909095331888</v>
+        <v>0.919588650965976</v>
       </c>
     </row>
     <row r="60">
@@ -4956,46 +4956,46 @@
         <v>62.056</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>0.988591444906425</v>
+        <v>-0.846437548885799</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>63.4116677555026</v>
+        <v>63.4988249109498</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>68.1122377717342</v>
+        <v>68.1604639161229</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>65.6407793314898</v>
+        <v>65.6391554841062</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>62.7721394108098</v>
+        <v>62.9024375488858</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>62.7721394108098</v>
+        <v>62.9024375488858</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>63.5138277736434</v>
+        <v>63.5851094020289</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>63.5138277736434</v>
+        <v>63.5851094020289</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>0.0204875231665361</v>
+        <v>0.0204018219606138</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>-0.0195837363627265</v>
+        <v>-0.0191375816912498</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>0.0206988330743894</v>
+        <v>0.020611361701766</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>1.00161106026315</v>
+        <v>1.00135883602886</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>0.932487756260461</v>
+        <v>0.932873776802278</v>
       </c>
     </row>
     <row r="61">
@@ -5015,46 +5015,46 @@
         <v>68.644</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1.04733532174737</v>
+        <v>3.20395424951462</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>65.4275767941949</v>
+        <v>65.4029710205324</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>68.5949327073371</v>
+        <v>68.646917575668</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>66.293823072303</v>
+        <v>66.2917879247853</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>65.5415687551477</v>
+        <v>65.4400457504854</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>65.5415687551477</v>
+        <v>65.4400457504854</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>65.5911414609501</v>
+        <v>65.569348308466</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>65.5911414609501</v>
+        <v>65.569348308466</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>0.0321830057192789</v>
+        <v>0.0307290213240475</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.0478760120970085</v>
+        <v>0.048844484863511</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>0.0327064792049696</v>
+        <v>0.0312060311776978</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>1.00249993465706</v>
+        <v>1.00254387966384</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>0.956209720924973</v>
+        <v>0.955168136081132</v>
       </c>
     </row>
     <row r="62">
@@ -5074,46 +5074,46 @@
         <v>67.255</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>0.981691695499709</v>
+        <v>-1.23986418400729</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>68.1104420869422</v>
+        <v>68.0799513471342</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>69.1463123661215</v>
+        <v>69.2027011040141</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>67.0578204380038</v>
+        <v>67.056575100961</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>68.5092889226951</v>
+        <v>68.4948641840073</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>68.5092889226951</v>
+        <v>68.4948641840073</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>68.2548614575671</v>
+        <v>68.1970280749987</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>68.2548614575671</v>
+        <v>68.1970280749987</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>0.0398080135493593</v>
+        <v>0.0392926519282474</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>0.108639405402034</v>
+        <v>0.10882720187577</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>0.0406109718063516</v>
+        <v>0.0400748190171267</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>1.00212037047771</v>
+        <v>1.00171969464648</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.98710775921304</v>
+        <v>0.985467720002665</v>
       </c>
     </row>
     <row r="63">
@@ -5133,46 +5133,46 @@
         <v>68.767</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.97598188956985</v>
+        <v>-1.59133818149478</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>71.790439701387</v>
+        <v>71.5098091601748</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>69.7590311892779</v>
+        <v>69.8203793220417</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>67.8925096370093</v>
+        <v>67.8932194928405</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>70.4592992297306</v>
+        <v>70.3583381814948</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>70.4592992297306</v>
+        <v>70.3583381814948</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>71.3114569049975</v>
+        <v>71.1047628785437</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>71.3114569049975</v>
+        <v>71.1047628785437</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>0.0438083387404195</v>
+        <v>0.0417533357250295</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>0.146010615313135</v>
+        <v>0.141310120363433</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>0.0447820914460513</v>
+        <v>0.0426372656642353</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>0.993328042029247</v>
+        <v>0.994335794118485</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>1.02225411805831</v>
+        <v>1.01839553965437</v>
       </c>
     </row>
     <row r="64">
@@ -5192,46 +5192,46 @@
         <v>77.802</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>1.02005761489572</v>
+        <v>1.28011004917431</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>0.83696958993803</v>
+        <v>0.597728401268138</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>73.4860434654854</v>
+        <v>73.254498000235</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>70.4253454783442</v>
+        <v>70.4920746525563</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>68.7648862201601</v>
+        <v>68.768615026046</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>76.2721623405102</v>
+        <v>76.5218899508257</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>75.8179402378335</v>
+        <v>75.207510967178</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>73.1344626869162</v>
+        <v>73.0210371574098</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>73.1344626869162</v>
+        <v>73.0210371574098</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>0.025242701029285</v>
+        <v>0.0265932568588975</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>0.15147307681659</v>
+        <v>0.148398388303784</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>0.0255639957594378</v>
+        <v>0.0269500129286606</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>0.995215679576839</v>
+        <v>0.996813016958707</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>1.03846792926852</v>
+        <v>1.03587584160799</v>
       </c>
     </row>
     <row r="65">
@@ -5251,46 +5251,46 @@
         <v>65.9</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.01475233829397</v>
+        <v>1.14190721013824</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>0.110726589945484</v>
+        <v>0</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>71.1275848134228</v>
+        <v>71.3107885137885</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>71.137949202384</v>
+        <v>71.2102457426508</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>69.6547796862604</v>
+        <v>69.6619812196434</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>64.941954320394</v>
+        <v>64.7580927898618</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>70.4426710422669</v>
+        <v>71.3107885137885</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>71.3606050632032</v>
+        <v>71.6807477968342</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>71.3606050632032</v>
+        <v>71.6807477968342</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>-0.0245537341850156</v>
+        <v>-0.0185253788251616</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>0.0879610184202688</v>
+        <v>0.0932051277926031</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>-0.0242547433664312</v>
+        <v>-0.0183548387252612</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>1.0032760883192</v>
+        <v>1.00518798474615</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>1.00312991677882</v>
+        <v>1.00660722413294</v>
       </c>
     </row>
     <row r="66">
@@ -5310,46 +5310,46 @@
         <v>67.304</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>0.979121967867891</v>
+        <v>-1.58990319258199</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>69.4272179520362</v>
+        <v>69.7057086117714</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>71.8929067021852</v>
+        <v>71.9702983871145</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>70.5772848042027</v>
+        <v>70.5847320724037</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>68.7391379304453</v>
+        <v>68.893903192582</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>68.7391379304453</v>
+        <v>68.893903192582</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>69.9509588855054</v>
+        <v>70.2276597873324</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>69.9509588855054</v>
+        <v>70.2276597873324</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>-0.019951558087078</v>
+        <v>-0.0204799535525997</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>0.0248494743336738</v>
+        <v>0.029775956073929</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>-0.0197538428443712</v>
+        <v>-0.0202716636497765</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>1.00754374075353</v>
+        <v>1.00748792582352</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.972988325194247</v>
+        <v>0.975786697584483</v>
       </c>
     </row>
     <row r="67">
@@ -5369,46 +5369,46 @@
         <v>70.755</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0.984309358454825</v>
+        <v>-1.05704425037695</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>70.5390108926394</v>
+        <v>70.4915265443079</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>72.685847769686</v>
+        <v>72.7677012199689</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>71.5514357996596</v>
+        <v>71.556525619569</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>71.8828886388641</v>
+        <v>71.8120442503769</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>71.8828886388641</v>
+        <v>71.8120442503769</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>70.6967618915094</v>
+        <v>70.691492368434</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>70.6967618915094</v>
+        <v>70.691492368434</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>0.0106053619943416</v>
+        <v>0.0065829839173224</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>-0.00861986334547915</v>
+        <v>-0.00581213540948855</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>0.0106617981781303</v>
+        <v>0.00660469938064701</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>1.00223636533705</v>
+        <v>1.00283673561815</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>0.972634481962992</v>
+        <v>0.971467989001622</v>
       </c>
     </row>
     <row r="68">
@@ -5428,46 +5428,46 @@
         <v>72.93</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>1.03767483360712</v>
+        <v>2.68202221959973</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>71.1870599806136</v>
+        <v>71.1628363197706</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>73.510431091342</v>
+        <v>73.5960001282384</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>72.5870761639349</v>
+        <v>72.5885657519823</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>70.2821323578639</v>
+        <v>70.2479777804003</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>70.2821323578639</v>
+        <v>70.2479777804003</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>71.4667763277718</v>
+        <v>71.4590320720306</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>71.4667763277718</v>
+        <v>71.4590320720306</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.0108329037966864</v>
+        <v>0.0107990760612771</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>-0.0228030164969367</v>
+        <v>-0.0213911654255482</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.010891792150878</v>
+        <v>0.0108575965491888</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>1.0039293145023</v>
+        <v>1.00416222522285</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>0.972199118774983</v>
+        <v>0.970963529913524</v>
       </c>
     </row>
     <row r="69">
@@ -5487,46 +5487,46 @@
         <v>66.714</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>0.99496973529098</v>
+        <v>-0.218085498161232</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>0.0256394031393836</v>
+        <v>0</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>73.5875375523418</v>
+        <v>73.5281284769447</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>74.3598135041521</v>
+        <v>74.448143713342</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>73.6957066525285</v>
+        <v>73.6933339536405</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>67.0512857162328</v>
+        <v>66.9320854981612</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>73.4199519564953</v>
+        <v>73.5281284769447</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>73.5234576791806</v>
+        <v>73.5492056725697</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>73.5234576791806</v>
+        <v>73.5492056725697</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.028371832433823</v>
+        <v>0.0288303396882569</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.030308776306784</v>
+        <v>0.0260663836966548</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.0287781463931729</v>
+        <v>0.0292499567924769</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>0.999129202100075</v>
+        <v>1.0002866548634</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>0.988752583074662</v>
+        <v>0.987925312896536</v>
       </c>
     </row>
     <row r="70">
@@ -5546,46 +5546,46 @@
         <v>75.119</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>0.975928917089613</v>
+        <v>-1.99032242444479</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>1</v>
+        <v>0.889702843521942</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>75.226089325542</v>
+        <v>75.144317383731</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>75.225134158407</v>
+        <v>75.3149880627311</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>74.8773033019096</v>
+        <v>74.8716087686826</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>76.9717944458677</v>
+        <v>77.1093224244448</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>76.9717944458677</v>
+        <v>76.892587955989</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>74.7171997869384</v>
+        <v>74.7131961587552</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>74.7171997869384</v>
+        <v>74.7131961587552</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0161058097351808</v>
+        <v>0.0157020847820387</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.0681368915790599</v>
+        <v>0.0638713632919885</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.0162362074015439</v>
+        <v>0.0158260102953047</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>0.993235198809798</v>
+        <v>0.994262756786063</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>0.993247810360842</v>
+        <v>0.992009666077692</v>
       </c>
     </row>
     <row r="71">
@@ -5605,46 +5605,46 @@
         <v>70.535</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>0.986430951756604</v>
+        <v>-1.00448024609826</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>72.4677421523481</v>
+        <v>72.3007837229392</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>76.0969447909299</v>
+        <v>76.1868142543341</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>76.1304633750678</v>
+        <v>76.1233427138642</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>71.5052582995227</v>
+        <v>71.5394802460983</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>71.5052582995227</v>
+        <v>71.5394802460983</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>72.4654276816316</v>
+        <v>72.3611495631953</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>72.4654276816316</v>
+        <v>72.3611495631953</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>-0.0306007285702215</v>
+        <v>-0.031987184819283</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.0250176350769282</v>
+        <v>0.0236189269574234</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>-0.0301372657397202</v>
+        <v>-0.0314810062543988</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>0.999968062055644</v>
+        <v>1.00083492649938</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>0.95227775412961</v>
+        <v>0.94978573748513</v>
       </c>
     </row>
     <row r="72">
@@ -5664,46 +5664,46 @@
         <v>73.632</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>1.05370109553723</v>
+        <v>4.15895019540416</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>69.5924577326419</v>
+        <v>69.3719750499756</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>76.9668888012235</v>
+        <v>77.0548893660131</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>77.464256590712</v>
+        <v>77.4585932018773</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>69.8793996816134</v>
+        <v>69.4730498045958</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>69.8793996816134</v>
+        <v>69.4730498045958</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>70.8700162157073</v>
+        <v>70.6556414573425</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>70.8700162157073</v>
+        <v>70.6556414573425</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>-0.0222621469319188</v>
+        <v>-0.0238515904038937</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>-0.00835017532241167</v>
+        <v>-0.011242674178377</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>-0.0220161740151947</v>
+        <v>-0.0235693893221436</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>1.01835771468186</v>
+        <v>1.01850410639804</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>0.920785773200966</v>
+        <v>0.916952084918662</v>
       </c>
     </row>
     <row r="73">
@@ -5723,46 +5723,46 @@
         <v>71.538</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>0.990611400070883</v>
+        <v>-0.598985974080169</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>73.4998509557089</v>
+        <v>73.3225270640287</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>77.8237397847336</v>
+        <v>77.9075758918748</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>78.8646266421737</v>
+        <v>78.8644983330753</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>72.2160072000798</v>
+        <v>72.1369859740802</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>72.2160072000798</v>
+        <v>72.1369859740802</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>74.2140399028949</v>
+        <v>74.0645710750449</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>74.2140399028949</v>
+        <v>74.0645710750449</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>0.04610590766287</v>
+        <v>0.0471193381020412</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.00939267881997186</v>
+        <v>0.00700708318686027</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>0.0471853100330799</v>
+        <v>0.0482470974346818</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>1.00971687612831</v>
+        <v>1.01012027327384</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>0.953616982532278</v>
+        <v>0.950672257828129</v>
       </c>
     </row>
     <row r="74">
@@ -5782,46 +5782,46 @@
         <v>79.132</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>0.958655811367494</v>
+        <v>-3.3792625474233</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>81.6295173359938</v>
+        <v>81.6063792502025</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>78.6518416562064</v>
+        <v>78.7284976763</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>80.2795929382385</v>
+        <v>80.288268490825</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>82.5447455298065</v>
+        <v>82.5112625474233</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>82.5447455298065</v>
+        <v>82.5112625474233</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>81.1790120905104</v>
+        <v>81.1473559570195</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>81.1790120905104</v>
+        <v>81.1473559570195</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>0.089703392672099</v>
+        <v>0.091329416440276</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.0864835984485284</v>
+        <v>0.0861181174018113</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>0.0938497917203918</v>
+        <v>0.0956298643085109</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.994481098747294</v>
+        <v>0.994375154278372</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.03213110311327</v>
+        <v>1.0307240497674</v>
       </c>
     </row>
     <row r="75">
@@ -5841,46 +5841,46 @@
         <v>86.477</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>0.989319937910748</v>
+        <v>-0.952912759151115</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>86.9081155393816</v>
+        <v>86.9783056257875</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>79.4320334975223</v>
+        <v>79.497671944971</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>81.623931790482</v>
+        <v>81.6434764966981</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>87.4105501023488</v>
+        <v>87.4299127591511</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>87.4105501023488</v>
+        <v>87.4299127591511</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>85.797184609399</v>
+        <v>85.8554266560115</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>85.797184609399</v>
+        <v>85.8554266560115</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>0.0553294505789794</v>
+        <v>0.0563980849874238</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.183974032228705</v>
+        <v>0.18648511216687</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>0.0568887499362472</v>
+        <v>0.0580187813079907</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>0.987217178475362</v>
+        <v>0.987090125960753</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.08013330178781</v>
+        <v>1.07997409930999</v>
       </c>
     </row>
     <row r="76">
@@ -5900,46 +5900,46 @@
         <v>91.623</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>1.06758228619692</v>
+        <v>5.57238144167969</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>86.1256759316116</v>
+        <v>86.2121652935068</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>80.147587455483</v>
+        <v>80.1974801516145</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>82.8237452734375</v>
+        <v>82.8548101425498</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>85.8228927030921</v>
+        <v>86.0506185583203</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>85.8228927030921</v>
+        <v>86.0506185583203</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>85.6725652161153</v>
+        <v>85.8031677060399</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>85.6725652161153</v>
+        <v>85.8031677060399</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>-0.00145354402571565</v>
+        <v>-0.000608870785412326</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>0.20886899412233</v>
+        <v>0.214385234303513</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>-0.0014524881422513</v>
+        <v>-0.000608685461210401</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>0.994738958962063</v>
+        <v>0.995255917931368</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.06893504765444</v>
+        <v>1.06989854972784</v>
       </c>
     </row>
     <row r="77">
@@ -5959,46 +5959,46 @@
         <v>83.511</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>0.998530197459879</v>
+        <v>-0.170520948367971</v>
       </c>
       <c r="G77" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>83.2933055611041</v>
+        <v>83.6362560647079</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>80.7867622497681</v>
+        <v>80.8152614004661</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>83.8340685531974</v>
+        <v>83.8758894015469</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>83.6339253559284</v>
+        <v>83.681520948368</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>83.6339253559284</v>
+        <v>83.681520948368</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>84.2434095816383</v>
+        <v>84.4302611551316</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>84.2434095816383</v>
+        <v>84.4302611551316</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>-0.0168223068970778</v>
+        <v>-0.0161300436309421</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>0.135141136257591</v>
+        <v>0.139954770946879</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>-0.0166816019909282</v>
+        <v>-0.0160006511136261</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1.01140672727699</v>
+        <v>1.00949355133507</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>1.0427872987555</v>
+        <v>1.04473164711739</v>
       </c>
     </row>
     <row r="78">
@@ -6018,46 +6018,46 @@
         <v>70.96</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>0.9339617071481</v>
+        <v>-5.26716112776548</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>83.8828949116042</v>
+        <v>84.3073841654703</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>81.341363665837</v>
+        <v>81.3420130072656</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>84.6249325330027</v>
+        <v>84.6763132889356</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>75.9774190493098</v>
+        <v>76.2271611277655</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>83.8828949116042</v>
+        <v>84.3073841654703</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>85.1012061171187</v>
+        <v>85.3296956708418</v>
       </c>
       <c r="N78" s="14" t="n">
-        <v>85.1012061171187</v>
+        <v>85.3296956708418</v>
       </c>
       <c r="O78" s="15" t="n">
-        <v>0.010130866795524</v>
+        <v>0.0105966442132189</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>0.048315370261407</v>
+        <v>0.0515400614659285</v>
       </c>
       <c r="Q78" s="17" t="n">
-        <v>0.0101823577623494</v>
+        <v>0.0106529874881895</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>1.01452395278916</v>
+        <v>1.0121260019569</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>1.04622300735856</v>
+        <v>1.04902365353584</v>
       </c>
     </row>
     <row r="79">
@@ -6077,46 +6077,46 @@
         <v>88.168</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>0.990594817578208</v>
+        <v>-0.854493404058741</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>88.2014472183073</v>
+        <v>88.6710552963076</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>81.8049769660904</v>
+        <v>81.7705236999702</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>85.1653674001077</v>
+        <v>85.2247089776959</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>89.0051092893378</v>
+        <v>89.0224934040587</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>89.0051092893378</v>
+        <v>89.0224934040587</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>88.3356493140698</v>
+        <v>88.6484030424275</v>
       </c>
       <c r="N79" s="14" t="n">
-        <v>88.3356493140698</v>
+        <v>88.6484030424275</v>
       </c>
       <c r="O79" s="15" t="n">
-        <v>0.0373025472062487</v>
+        <v>0.0381554921266497</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>0.0295868065627958</v>
+        <v>0.032531157262853</v>
       </c>
       <c r="Q79" s="17" t="n">
-        <v>0.0380070194598632</v>
+        <v>0.0388927599646851</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>1.00152154074559</v>
+        <v>0.999744536096876</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>1.07983221302888</v>
+        <v>1.08411196396019</v>
       </c>
     </row>
     <row r="80">
@@ -6136,46 +6136,46 @@
         <v>99.067</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>1.08329753127412</v>
+        <v>6.8257588038777</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>91.5257552195274</v>
+        <v>92.0377213423232</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>82.1727758699575</v>
+        <v>82.0954355635107</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>85.4206931536601</v>
+        <v>85.4878589951905</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>91.4494837659995</v>
+        <v>92.2412411961223</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>91.4494837659995</v>
+        <v>92.2412411961223</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>90.3178165793879</v>
+        <v>90.7905761366955</v>
       </c>
       <c r="N80" s="14" t="n">
-        <v>90.3178165793879</v>
+        <v>90.7905761366955</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>0.0221909896489051</v>
+        <v>0.0238774750080564</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>0.0542209907168592</v>
+        <v>0.0581261573901595</v>
       </c>
       <c r="Q80" s="17" t="n">
-        <v>0.0224390410973334</v>
+        <v>0.0241648244158745</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>0.986802199695132</v>
+        <v>0.986449629701401</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>1.09912091472144</v>
+        <v>1.10591503064087</v>
       </c>
     </row>
     <row r="81">
@@ -6195,46 +6195,46 @@
         <v>89.526</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1.00177705603903</v>
+        <v>-0.131328750478532</v>
       </c>
       <c r="G81" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>88.3608383271726</v>
+        <v>88.5954123234603</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>82.4444341795698</v>
+        <v>82.3159231638836</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>85.3754285022535</v>
+        <v>85.4515347909141</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>89.3671894962146</v>
+        <v>89.6573287504785</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>89.3671894962146</v>
+        <v>89.6573287504785</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>87.9705313971834</v>
+        <v>88.0750716447829</v>
       </c>
       <c r="N81" s="14" t="n">
-        <v>87.9705313971834</v>
+        <v>88.0750716447829</v>
       </c>
       <c r="O81" s="15" t="n">
-        <v>-0.0263328573631497</v>
+        <v>-0.0303659555012539</v>
       </c>
       <c r="P81" s="16" t="n">
-        <v>0.0442422954395409</v>
+        <v>0.0431694802288278</v>
       </c>
       <c r="Q81" s="17" t="n">
-        <v>-0.0259891710307375</v>
+        <v>-0.0299095413583906</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>0.995582806395023</v>
+        <v>0.994126776262661</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>1.06702814171272</v>
+        <v>1.06996396638149</v>
       </c>
     </row>
     <row r="82">
@@ -6254,46 +6254,46 @@
         <v>69.779</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>0.916194654780322</v>
+        <v>-6.39505423796944</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>0</v>
+        <v>0.110560153501116</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>81.6982628303047</v>
+        <v>81.3124946418629</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>82.6254236394936</v>
+        <v>82.4375021956052</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>85.0442361075431</v>
+        <v>85.1352747253658</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>76.1617628261879</v>
+        <v>76.1740542379694</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>81.6982628303047</v>
+        <v>80.7443878820521</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>82.9461042230634</v>
+        <v>82.5146632129903</v>
       </c>
       <c r="N82" s="14" t="n">
-        <v>82.9461042230634</v>
+        <v>82.5146632129903</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>-0.0588108377403786</v>
+        <v>-0.0652135242164346</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>-0.0253239876658071</v>
+        <v>-0.0329900679443472</v>
       </c>
       <c r="Q82" s="17" t="n">
-        <v>-0.0571148894330858</v>
+        <v>-0.0631326018583142</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>1.01527378122287</v>
+        <v>1.01478454912031</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>1.00388113693636</v>
+        <v>1.00093599412076</v>
       </c>
     </row>
     <row r="83">
@@ -6313,46 +6313,46 @@
         <v>78.684</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>0.995739069281401</v>
+        <v>-0.228548337378425</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>80.7426544991856</v>
+        <v>80.683768614732</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>82.7255427163681</v>
+        <v>82.4702767316835</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>84.4617374361543</v>
+        <v>84.5796461288428</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>79.0207017354297</v>
+        <v>78.9125483373784</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>79.0207017354297</v>
+        <v>78.9125483373784</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>81.9284793457735</v>
+        <v>81.8507104915952</v>
       </c>
       <c r="N83" s="14" t="n">
-        <v>81.9284793457735</v>
+        <v>81.8507104915952</v>
       </c>
       <c r="O83" s="15" t="n">
-        <v>-0.0123443865961455</v>
+        <v>-0.00807902927259475</v>
       </c>
       <c r="P83" s="16" t="n">
-        <v>-0.0725320979474119</v>
+        <v>-0.0766815003715172</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>-0.0122685072050317</v>
+        <v>-0.0080464816257112</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>1.01468647338811</v>
+        <v>1.01446315531486</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>0.990364966557821</v>
+        <v>0.992487399525722</v>
       </c>
     </row>
     <row r="84">
@@ -6372,46 +6372,46 @@
         <v>95.838</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>1.08938693789785</v>
+        <v>7.0046425904281</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>86.5567396236961</v>
+        <v>87.4077002695248</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>82.7540104013269</v>
+        <v>82.4232926486807</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>83.6458240883258</v>
+        <v>83.8032618974255</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>87.9742510819297</v>
+        <v>88.8333574095719</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>87.9742510819297</v>
+        <v>88.8333574095719</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>86.1622300190654</v>
+        <v>86.7773749479423</v>
       </c>
       <c r="N84" s="14" t="n">
-        <v>86.1622300190654</v>
+        <v>86.7773749479423</v>
       </c>
       <c r="O84" s="15" t="n">
-        <v>0.0503852512408347</v>
+        <v>0.0584489462176019</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>-0.0460107066103592</v>
+        <v>-0.0442028386592775</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>0.0516761778944252</v>
+        <v>0.0601908575595438</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>0.995442185018222</v>
+        <v>0.992788675143736</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>1.04118494803104</v>
+        <v>1.05282587190274</v>
       </c>
     </row>
     <row r="85">
@@ -6431,46 +6431,46 @@
         <v>89.752</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1.00080602198701</v>
+        <v>-0.778236635246835</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>89.2503992405649</v>
+        <v>89.5731583327917</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>82.7177301598905</v>
+        <v>82.3033722429128</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>82.5871824857932</v>
+        <v>82.7963994382371</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>89.6797161769725</v>
+        <v>90.5302366352468</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>89.6797161769725</v>
+        <v>90.5302366352468</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>88.1034093831974</v>
+        <v>88.3669947059173</v>
       </c>
       <c r="N85" s="14" t="n">
-        <v>88.1034093831974</v>
+        <v>88.3669947059173</v>
       </c>
       <c r="O85" s="15" t="n">
-        <v>0.02227931639375</v>
+        <v>0.0181526064635045</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>0.00151048292994949</v>
+        <v>0.00331447997353673</v>
       </c>
       <c r="Q85" s="17" t="n">
-        <v>0.0225293537980906</v>
+        <v>0.0183183664973576</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>0.987148630514516</v>
+        <v>0.98653431843507</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>1.06510912730435</v>
+        <v>1.07367404636967</v>
       </c>
     </row>
     <row r="86">
@@ -6490,46 +6490,46 @@
         <v>77.378</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>0.909473927452505</v>
+        <v>-6.19614814360361</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>85.9360866743142</v>
+        <v>85.166164107375</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>82.6268681080047</v>
+        <v>82.1213441011708</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>81.2981411852597</v>
+        <v>81.5744866359615</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>85.0799540969149</v>
+        <v>83.5741481436036</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>85.0799540969149</v>
+        <v>83.5741481436036</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>85.2010835223796</v>
+        <v>84.5622704906476</v>
       </c>
       <c r="N86" s="14" t="n">
-        <v>85.2010835223796</v>
+        <v>84.5622704906476</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>-0.0334970800548467</v>
+        <v>-0.0440103450232556</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>0.0271860784835891</v>
+        <v>0.0248150716239606</v>
       </c>
       <c r="Q86" s="17" t="n">
-        <v>-0.0329422650171735</v>
+        <v>-0.0430559421866917</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>0.991447095389389</v>
+        <v>0.992909230760164</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>1.03115470153135</v>
+        <v>1.02972341010967</v>
       </c>
     </row>
     <row r="87">
@@ -6549,46 +6549,46 @@
         <v>81.338</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>1.00461053071864</v>
+        <v>0.767450959863544</v>
       </c>
       <c r="G87" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>79.995729620018</v>
+        <v>79.1460242125935</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>82.4959416028759</v>
+        <v>81.8931786004913</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>79.8264914118847</v>
+        <v>80.1916205612677</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>80.9647097187161</v>
+        <v>80.5705490401365</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>80.9647097187161</v>
+        <v>80.5705490401365</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>79.8683477784664</v>
+        <v>79.2896003583325</v>
       </c>
       <c r="N87" s="14" t="n">
-        <v>79.8683477784664</v>
+        <v>79.2896003583325</v>
       </c>
       <c r="O87" s="15" t="n">
-        <v>-0.06463452482244</v>
+        <v>-0.0643812148292535</v>
       </c>
       <c r="P87" s="16" t="n">
-        <v>-0.025145487671173</v>
+        <v>-0.0312900171285102</v>
       </c>
       <c r="Q87" s="17" t="n">
-        <v>-0.0625899991343711</v>
+        <v>-0.0623525137359965</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>0.998407641980932</v>
+        <v>1.00181406643186</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>0.968148811040203</v>
+        <v>0.968207629907001</v>
       </c>
     </row>
     <row r="88">
@@ -6608,46 +6608,46 @@
         <v>78.735</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>1.08653925948282</v>
+        <v>6.29184479054667</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>72.6357453294825</v>
+        <v>72.8590692692117</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>82.3410011804539</v>
+        <v>81.6357541204373</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>78.2389334553856</v>
+        <v>78.7118965923628</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>72.4640175795184</v>
+        <v>72.4431552094533</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>72.4640175795184</v>
+        <v>72.4431552094533</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>73.449310800074</v>
+        <v>73.7433033640071</v>
       </c>
       <c r="N88" s="14" t="n">
-        <v>73.449310800074</v>
+        <v>73.7433033640071</v>
       </c>
       <c r="O88" s="15" t="n">
-        <v>-0.0837841070078302</v>
+        <v>-0.0725167877652945</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>-0.147546311373074</v>
+        <v>-0.150201266076029</v>
       </c>
       <c r="Q88" s="17" t="n">
-        <v>-0.0803702237111142</v>
+        <v>-0.0699498669341259</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>1.0112006212217</v>
+        <v>1.01213622550582</v>
       </c>
       <c r="S88" s="19" t="n">
-        <v>0.892013817503951</v>
+        <v>0.903321150867468</v>
       </c>
     </row>
     <row r="89">
@@ -6667,80 +6667,106 @@
         <v>67.604</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>0.995574691957585</v>
+        <v>-1.91235399698524</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>69.5610633792303</v>
+        <v>71.1379770595526</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>82.1771403567604</v>
+        <v>81.3651223970965</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>76.6078586970142</v>
+        <v>77.2013047498482</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>67.9044983225429</v>
+        <v>69.5163539969852</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>67.9044983225429</v>
+        <v>69.5163539969852</v>
       </c>
       <c r="M89" s="13" t="n">
-        <v>69.4243380748681</v>
+        <v>71.9815106415767</v>
       </c>
       <c r="N89" s="14" t="n">
-        <v>69.4243380748681</v>
+        <v>71.9815106415767</v>
       </c>
       <c r="O89" s="15" t="n">
-        <v>-0.0563580205670745</v>
+        <v>-0.0241808998598372</v>
       </c>
       <c r="P89" s="16" t="n">
-        <v>-0.212013036034581</v>
+        <v>-0.18542538556246</v>
       </c>
       <c r="Q89" s="17" t="n">
-        <v>-0.0547993259754564</v>
+        <v>-0.0238908842167528</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>0.998034456379472</v>
+        <v>1.01185771112549</v>
       </c>
       <c r="S89" s="19" t="n">
-        <v>0.84481326283042</v>
+        <v>0.884672799854909</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
         <v>142</v>
       </c>
-      <c r="B90" s="2"/>
+      <c r="B90" s="2" t="n">
+        <v>71.462</v>
+      </c>
       <c r="C90" s="3" t="n">
-        <v>66.8246651811335</v>
+        <v>71.462</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>78.6149812648757</v>
+        <v>71.462</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>56.8026068914901</v>
+        <v>71.462</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>0.911983259585936</v>
-      </c>
-      <c r="G90" s="7"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="9"/>
-      <c r="J90" s="10"/>
-      <c r="K90" s="11"/>
-      <c r="L90" s="12"/>
-      <c r="M90" s="13"/>
+        <v>-4.98817936288306</v>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="8" t="n">
+        <v>75.3119203312039</v>
+      </c>
+      <c r="I90" s="9" t="n">
+        <v>81.0915897922374</v>
+      </c>
+      <c r="J90" s="10" t="n">
+        <v>75.6944913474111</v>
+      </c>
+      <c r="K90" s="11" t="n">
+        <v>76.4501793628831</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>76.4501793628831</v>
+      </c>
+      <c r="M90" s="13" t="n">
+        <v>74.1389042409171</v>
+      </c>
       <c r="N90" s="14" t="n">
-        <v>73.2740041867365</v>
-      </c>
-      <c r="O90" s="15"/>
-      <c r="P90" s="16"/>
-      <c r="Q90" s="17"/>
-      <c r="R90" s="18"/>
-      <c r="S90" s="19"/>
+        <v>74.1389042409171</v>
+      </c>
+      <c r="O90" s="15" t="n">
+        <v>0.0295311286262032</v>
+      </c>
+      <c r="P90" s="16" t="n">
+        <v>-0.12326261096411</v>
+      </c>
+      <c r="Q90" s="17" t="n">
+        <v>0.0299714965705968</v>
+      </c>
+      <c r="R90" s="18" t="n">
+        <v>0.98442456273684</v>
+      </c>
+      <c r="S90" s="19" t="n">
+        <v>0.914261323903828</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
@@ -6748,16 +6774,16 @@
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3" t="n">
-        <v>72.7828104533536</v>
+        <v>77.2270113134063</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>89.0149265895745</v>
+        <v>88.3660511232155</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>59.5106652383537</v>
+        <v>66.087971503597</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>1.01087869915918</v>
+        <v>1.40730775535957</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="8"/>
@@ -6767,7 +6793,7 @@
       <c r="L91" s="12"/>
       <c r="M91" s="13"/>
       <c r="N91" s="14" t="n">
-        <v>71.9995490199687</v>
+        <v>75.8197035580467</v>
       </c>
       <c r="O91" s="15"/>
       <c r="P91" s="16"/>
@@ -6781,16 +6807,16 @@
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="3" t="n">
-        <v>71.8463563171369</v>
+        <v>70.3658051842256</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>88.3915045537389</v>
+        <v>84.3626417435545</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>58.3981338716862</v>
+        <v>56.3689686248967</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>1.08083521492496</v>
+        <v>5.45978224290625</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="8"/>
@@ -6800,7 +6826,7 @@
       <c r="L92" s="12"/>
       <c r="M92" s="13"/>
       <c r="N92" s="14" t="n">
-        <v>66.4729972941574</v>
+        <v>64.9060229413193</v>
       </c>
       <c r="O92" s="15"/>
       <c r="P92" s="16"/>
@@ -6814,16 +6840,16 @@
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="3" t="n">
-        <v>65.932906002413</v>
+        <v>63.9565785628456</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>81.437894807991</v>
+        <v>78.264870945832</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>53.3799173489499</v>
+        <v>49.6482861798591</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>0.994546580300595</v>
+        <v>-2.48277984285024</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="8"/>
@@ -6833,7 +6859,7 @@
       <c r="L93" s="12"/>
       <c r="M93" s="13"/>
       <c r="N93" s="14" t="n">
-        <v>66.2944373932544</v>
+        <v>66.4393584056958</v>
       </c>
       <c r="O93" s="15"/>
       <c r="P93" s="16"/>
@@ -6846,10 +6872,18 @@
         <v>146</v>
       </c>
       <c r="B94" s="2"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="6"/>
+      <c r="C94" s="3" t="n">
+        <v>68.5095756163749</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>83.0890714926517</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>53.9300797400981</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>-3.96571309231863</v>
+      </c>
       <c r="G94" s="7"/>
       <c r="H94" s="8"/>
       <c r="I94" s="9"/>
@@ -6857,7 +6891,9 @@
       <c r="K94" s="11"/>
       <c r="L94" s="12"/>
       <c r="M94" s="13"/>
-      <c r="N94" s="14"/>
+      <c r="N94" s="14" t="n">
+        <v>72.4752887086935</v>
+      </c>
       <c r="O94" s="15"/>
       <c r="P94" s="16"/>
       <c r="Q94" s="17"/>
@@ -7355,7 +7391,7 @@
         <v>183</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.0242900109349527</v>
+        <v>0.025849096407696</v>
       </c>
     </row>
     <row r="6">
@@ -7363,7 +7399,7 @@
         <v>184</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>-0.0849296970804645</v>
+        <v>-0.111867292920452</v>
       </c>
     </row>
     <row r="7">
@@ -7371,7 +7407,7 @@
         <v>185</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>-0.114400378270245</v>
+        <v>-0.143195647707597</v>
       </c>
     </row>
     <row r="8">
@@ -7379,7 +7415,7 @@
         <v>186</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>-0.0130936923381602</v>
+        <v>-0.00769417379355677</v>
       </c>
     </row>
     <row r="9">
@@ -7387,7 +7423,7 @@
         <v>187</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.0929662219618596</v>
+        <v>0.118172102637433</v>
       </c>
     </row>
     <row r="10">
@@ -7395,7 +7431,7 @@
         <v>188</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>-0.0083870450536254</v>
+        <v>0.0210359782689025</v>
       </c>
     </row>
     <row r="11">
@@ -7403,7 +7439,7 @@
         <v>189</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>-0.257445905891771</v>
+        <v>-0.253080798826828</v>
       </c>
     </row>
     <row r="12">
@@ -7411,7 +7447,7 @@
         <v>190</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.393353214444826</v>
+        <v>-0.405851428014495</v>
       </c>
     </row>
     <row r="13">
@@ -7419,7 +7455,7 @@
         <v>191</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.229744332195104</v>
+        <v>-0.206158655307675</v>
       </c>
     </row>
     <row r="14">
@@ -7477,4 +7513,237 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
+    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
+    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C434A20-B83E-48FD-9840-428951A22ECD}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18CB26EA-E75A-4228-B1E2-835F3C1A06E9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9A8C3BA-F9FA-441E-92A9-541475A4CA29}"/>
 </file>